--- a/odcs-template-v3.2.xlsx
+++ b/odcs-template-v3.2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakob/entropyData/open-data-contract-standard-excel-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBACBCCE-EAC4-F945-B861-C87BF230602B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3951829-6F38-7B4C-88E7-5B20E0EEFA80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="-33240" windowWidth="60160" windowHeight="33240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="-33240" windowWidth="60160" windowHeight="33240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="8" r:id="rId1"/>
@@ -14370,10 +14370,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
-      <c r="B5" s="5" t="str">
-        <f>IF(owner &lt;&gt; "", owner, "")</f>
-        <v/>
-      </c>
+      <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">
         <v>48</v>
       </c>
@@ -14381,18 +14378,9 @@
         <f>IF(owner &lt;&gt; "", owner, "")</f>
         <v/>
       </c>
-      <c r="E5" s="5" t="str">
-        <f>IF(owner &lt;&gt; "", owner, "")</f>
-        <v/>
-      </c>
-      <c r="F5" s="5" t="str">
-        <f>IF(owner &lt;&gt; "", owner, "")</f>
-        <v/>
-      </c>
-      <c r="G5" s="5" t="str">
-        <f>IF(owner &lt;&gt; "", owner, "")</f>
-        <v/>
-      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>

--- a/odcs-template-v3.2.xlsx
+++ b/odcs-template-v3.2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakob/entropyData/open-data-contract-standard-excel-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3951829-6F38-7B4C-88E7-5B20E0EEFA80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1031AD6A-ED8F-9542-9505-273B1DC3029A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-33240" windowWidth="60160" windowHeight="33240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="8" r:id="rId1"/>
@@ -57,9 +57,9 @@
     <definedName name="price.priceAmount">Pricing!$B$4</definedName>
     <definedName name="price.priceCurrency">Pricing!$B$5</definedName>
     <definedName name="price.priceUnit">Pricing!$B$6</definedName>
-    <definedName name="quality">Quality!$A$4:$AZ$300</definedName>
+    <definedName name="quality">Quality!$A$4:$BF$300</definedName>
     <definedName name="relationships">Relationships!$A$4:$AZ$300</definedName>
-    <definedName name="roles" localSheetId="7">Roles!$A$4:$AZ$1000</definedName>
+    <definedName name="roles" localSheetId="7">Roles!$C$4:$BB$1000</definedName>
     <definedName name="schema.businessName" localSheetId="2">'Schema &lt;table_name&gt;'!$B$8</definedName>
     <definedName name="schema.context.instructions" localSheetId="2">'Schema &lt;table_name&gt;'!$B$13</definedName>
     <definedName name="schema.dataGranularityDescription" localSheetId="2">'Schema &lt;table_name&gt;'!$B$10</definedName>
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="249">
   <si>
     <t>Property</t>
   </si>
@@ -420,11 +420,6 @@
   </si>
   <si>
     <t>Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This section lists team members and the history of their relation with this data contract.
-This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
-</t>
   </si>
   <si>
     <t>Access</t>
@@ -894,6 +889,22 @@
   </si>
   <si>
     <t>It can override the columns for custom properties in the other sheets.</t>
+  </si>
+  <si>
+    <t>Dimension</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Business Impact</t>
+  </si>
+  <si>
+    <t>Server name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
+</t>
   </si>
 </sst>
 </file>
@@ -1113,7 +1124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1216,6 +1227,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1679,7 +1691,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1830,7 +1842,7 @@
     </row>
     <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -1843,10 +1855,10 @@
     </row>
     <row r="18" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>128</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>129</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -1859,7 +1871,7 @@
     <row r="19" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="23"/>
       <c r="B19" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -1882,10 +1894,10 @@
     </row>
     <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -1898,7 +1910,7 @@
     <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="25"/>
       <c r="B22" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -1911,7 +1923,7 @@
     <row r="23" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="13"/>
       <c r="B23" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -1963,7 +1975,7 @@
         <v>37</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -2039,7 +2051,7 @@
   <sheetData>
     <row r="1" spans="1:52" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2095,7 +2107,7 @@
     </row>
     <row r="2" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2205,7 +2217,7 @@
     </row>
     <row r="4" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="5"/>
@@ -2261,7 +2273,7 @@
     </row>
     <row r="5" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="5"/>
@@ -2427,7 +2439,7 @@
     </row>
     <row r="8" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="5"/>
@@ -2537,7 +2549,7 @@
     </row>
     <row r="10" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -2594,7 +2606,7 @@
     <row r="11" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -2650,7 +2662,7 @@
     <row r="12" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -2706,7 +2718,7 @@
     <row r="13" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -2762,7 +2774,7 @@
     <row r="14" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -2818,7 +2830,7 @@
     <row r="15" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -2874,7 +2886,7 @@
     <row r="16" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -2930,7 +2942,7 @@
     <row r="17" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -2986,7 +2998,7 @@
     <row r="18" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -3098,7 +3110,7 @@
     <row r="20" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -3154,7 +3166,7 @@
     <row r="21" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -3210,7 +3222,7 @@
     <row r="22" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -3266,7 +3278,7 @@
     <row r="23" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -3322,7 +3334,7 @@
     <row r="24" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -3378,7 +3390,7 @@
     <row r="25" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -3434,7 +3446,7 @@
     <row r="26" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -3490,7 +3502,7 @@
     <row r="27" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -3602,7 +3614,7 @@
     <row r="29" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -3658,7 +3670,7 @@
     <row r="30" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -3714,7 +3726,7 @@
     <row r="31" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -3770,7 +3782,7 @@
     <row r="32" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -3826,7 +3838,7 @@
     <row r="33" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -4045,7 +4057,7 @@
     </row>
     <row r="37" spans="1:52" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -13011,7 +13023,7 @@
     </row>
     <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B7" s="5"/>
     </row>
@@ -13041,13 +13053,13 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A1" s="29" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B1" s="29"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B2" s="31"/>
     </row>
@@ -13060,10 +13072,10 @@
         <v>55</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D4" s="33" t="s">
         <v>18</v>
@@ -13244,13 +13256,13 @@
   <sheetData>
     <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.2">
       <c r="A1" s="29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B1" s="29"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B2" s="31"/>
     </row>
@@ -13268,13 +13280,13 @@
         <v>55</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C4" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>230</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>231</v>
       </c>
       <c r="E4" s="33" t="s">
         <v>12</v>
@@ -13506,13 +13518,13 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.2">
       <c r="A1" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B1" s="29"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B2" s="31"/>
     </row>
@@ -13530,10 +13542,10 @@
         <v>55</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D4" s="33" t="s">
         <v>12</v>
@@ -13750,13 +13762,13 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.2">
       <c r="A1" s="29" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B1" s="29"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B2" s="31"/>
     </row>
@@ -13780,7 +13792,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E4" s="33" t="s">
         <v>3</v>
@@ -14032,13 +14044,13 @@
   <sheetData>
     <row r="1" spans="1:11" ht="24" x14ac:dyDescent="0.2">
       <c r="A1" s="29" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B1" s="29"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B2" s="31"/>
     </row>
@@ -14059,13 +14071,13 @@
         <v>0</v>
       </c>
       <c r="C4" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>225</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="E4" s="33" t="s">
         <v>226</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>227</v>
       </c>
       <c r="F4" s="32" t="s">
         <v>24</v>
@@ -14342,7 +14354,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -14350,7 +14362,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>0</v>
@@ -14362,7 +14374,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>22</v>
@@ -14544,341 +14556,341 @@
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" t="s">
         <v>169</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>170</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>171</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>172</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>173</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>174</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>175</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>176</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>177</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>178</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>179</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>180</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>181</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>182</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>183</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>184</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>185</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>186</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>187</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>188</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>189</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>190</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>191</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>192</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>193</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>194</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>195</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>196</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>197</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>198</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>199</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>200</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>201</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>202</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>203</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>204</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>205</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>206</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>207</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>208</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>209</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>210</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>211</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>212</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N2" t="s">
+        <v>213</v>
+      </c>
+      <c r="AG2" t="s">
         <v>214</v>
       </c>
-      <c r="AG2" t="s">
-        <v>215</v>
-      </c>
       <c r="AJ2" t="s">
+        <v>213</v>
+      </c>
+      <c r="AS2" t="s">
         <v>214</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H3" t="s">
+        <v>213</v>
+      </c>
+      <c r="S3" t="s">
+        <v>213</v>
+      </c>
+      <c r="AE3" t="s">
         <v>214</v>
       </c>
-      <c r="S3" t="s">
+      <c r="AN3" t="s">
+        <v>213</v>
+      </c>
+      <c r="AS3" t="s">
         <v>214</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>215</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>214</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G5" t="s">
+        <v>213</v>
+      </c>
+      <c r="I5" t="s">
         <v>214</v>
       </c>
-      <c r="G5" t="s">
+      <c r="K5" t="s">
+        <v>213</v>
+      </c>
+      <c r="M5" t="s">
+        <v>213</v>
+      </c>
+      <c r="N5" t="s">
+        <v>213</v>
+      </c>
+      <c r="O5" t="s">
         <v>214</v>
       </c>
-      <c r="I5" t="s">
-        <v>215</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="P5" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>213</v>
+      </c>
+      <c r="R5" t="s">
+        <v>213</v>
+      </c>
+      <c r="T5" t="s">
+        <v>213</v>
+      </c>
+      <c r="U5" t="s">
+        <v>213</v>
+      </c>
+      <c r="V5" t="s">
+        <v>213</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AM5" t="s">
         <v>214</v>
       </c>
-      <c r="M5" t="s">
+      <c r="AO5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AS5" t="s">
         <v>214</v>
-      </c>
-      <c r="N5" t="s">
-        <v>214</v>
-      </c>
-      <c r="O5" t="s">
-        <v>215</v>
-      </c>
-      <c r="P5" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>214</v>
-      </c>
-      <c r="R5" t="s">
-        <v>214</v>
-      </c>
-      <c r="T5" t="s">
-        <v>214</v>
-      </c>
-      <c r="U5" t="s">
-        <v>214</v>
-      </c>
-      <c r="V5" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>214</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>214</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>214</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>214</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>214</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>214</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>214</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>215</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>214</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>214</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>214</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>214</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
+        <v>213</v>
+      </c>
+      <c r="AS6" t="s">
         <v>214</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AH7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AI7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AS7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="W8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="X8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Y8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AH8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AI8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AS8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AH9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AS9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:45" x14ac:dyDescent="0.2">
@@ -14886,299 +14898,299 @@
         <v>80</v>
       </c>
       <c r="D10" t="s">
+        <v>213</v>
+      </c>
+      <c r="N10" t="s">
         <v>214</v>
       </c>
-      <c r="N10" t="s">
-        <v>215</v>
-      </c>
       <c r="W10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="X10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Y10" t="s">
+        <v>213</v>
+      </c>
+      <c r="AH10" t="s">
         <v>214</v>
       </c>
-      <c r="AH10" t="s">
-        <v>215</v>
-      </c>
       <c r="AI10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AS10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F11" t="s">
+        <v>213</v>
+      </c>
+      <c r="G11" t="s">
+        <v>213</v>
+      </c>
+      <c r="H11" t="s">
         <v>214</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
+        <v>213</v>
+      </c>
+      <c r="J11" t="s">
+        <v>213</v>
+      </c>
+      <c r="L11" t="s">
+        <v>213</v>
+      </c>
+      <c r="M11" t="s">
         <v>214</v>
       </c>
-      <c r="H11" t="s">
-        <v>215</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="O11" t="s">
+        <v>213</v>
+      </c>
+      <c r="P11" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>213</v>
+      </c>
+      <c r="R11" t="s">
+        <v>213</v>
+      </c>
+      <c r="T11" t="s">
+        <v>213</v>
+      </c>
+      <c r="U11" t="s">
+        <v>213</v>
+      </c>
+      <c r="V11" t="s">
+        <v>213</v>
+      </c>
+      <c r="W11" t="s">
+        <v>213</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>213</v>
+      </c>
+      <c r="AB11" t="s">
         <v>214</v>
       </c>
-      <c r="J11" t="s">
+      <c r="AC11" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>213</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>213</v>
+      </c>
+      <c r="AG11" t="s">
         <v>214</v>
       </c>
-      <c r="L11" t="s">
+      <c r="AJ11" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>213</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>213</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>213</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>213</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>213</v>
+      </c>
+      <c r="AP11" t="s">
         <v>214</v>
       </c>
-      <c r="M11" t="s">
-        <v>215</v>
-      </c>
-      <c r="O11" t="s">
+      <c r="AQ11" t="s">
+        <v>213</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>213</v>
+      </c>
+      <c r="AS11" t="s">
         <v>214</v>
-      </c>
-      <c r="P11" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>214</v>
-      </c>
-      <c r="R11" t="s">
-        <v>214</v>
-      </c>
-      <c r="T11" t="s">
-        <v>214</v>
-      </c>
-      <c r="U11" t="s">
-        <v>214</v>
-      </c>
-      <c r="V11" t="s">
-        <v>214</v>
-      </c>
-      <c r="W11" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>214</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>214</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>214</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>215</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>214</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>214</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>214</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>214</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>214</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>214</v>
-      </c>
-      <c r="AP11" t="s">
-        <v>215</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>214</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>214</v>
-      </c>
-      <c r="AS11" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D12" t="s">
+        <v>213</v>
+      </c>
+      <c r="N12" t="s">
         <v>214</v>
       </c>
-      <c r="D12" t="s">
+      <c r="AH12" t="s">
+        <v>213</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>213</v>
+      </c>
+      <c r="AS12" t="s">
         <v>214</v>
-      </c>
-      <c r="N12" t="s">
-        <v>215</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>214</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>214</v>
-      </c>
-      <c r="AS12" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Y14" t="s">
+        <v>213</v>
+      </c>
+      <c r="AS14" t="s">
         <v>214</v>
-      </c>
-      <c r="AS14" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G15" t="s">
+        <v>213</v>
+      </c>
+      <c r="I15" t="s">
+        <v>213</v>
+      </c>
+      <c r="J15" t="s">
+        <v>213</v>
+      </c>
+      <c r="L15" t="s">
         <v>214</v>
       </c>
-      <c r="I15" t="s">
+      <c r="M15" t="s">
         <v>214</v>
       </c>
-      <c r="J15" t="s">
+      <c r="O15" t="s">
         <v>214</v>
       </c>
-      <c r="L15" t="s">
-        <v>215</v>
-      </c>
-      <c r="M15" t="s">
-        <v>215</v>
-      </c>
-      <c r="O15" t="s">
-        <v>215</v>
-      </c>
       <c r="P15" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>213</v>
+      </c>
+      <c r="R15" t="s">
         <v>214</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="T15" t="s">
         <v>214</v>
       </c>
-      <c r="R15" t="s">
-        <v>215</v>
-      </c>
-      <c r="T15" t="s">
-        <v>215</v>
-      </c>
       <c r="U15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="V15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Z15" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>213</v>
+      </c>
+      <c r="AB15" t="s">
         <v>214</v>
       </c>
-      <c r="AA15" t="s">
+      <c r="AC15" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>213</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK15" t="s">
         <v>214</v>
       </c>
-      <c r="AB15" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC15" t="s">
+      <c r="AL15" t="s">
+        <v>213</v>
+      </c>
+      <c r="AM15" t="s">
         <v>214</v>
       </c>
-      <c r="AD15" t="s">
+      <c r="AN15" t="s">
+        <v>213</v>
+      </c>
+      <c r="AO15" t="s">
         <v>214</v>
       </c>
-      <c r="AJ15" t="s">
+      <c r="AP15" t="s">
         <v>214</v>
       </c>
-      <c r="AK15" t="s">
-        <v>215</v>
-      </c>
-      <c r="AL15" t="s">
+      <c r="AQ15" t="s">
+        <v>213</v>
+      </c>
+      <c r="AR15" t="s">
         <v>214</v>
       </c>
-      <c r="AM15" t="s">
-        <v>215</v>
-      </c>
-      <c r="AN15" t="s">
+      <c r="AS15" t="s">
         <v>214</v>
-      </c>
-      <c r="AO15" t="s">
-        <v>215</v>
-      </c>
-      <c r="AP15" t="s">
-        <v>215</v>
-      </c>
-      <c r="AQ15" t="s">
-        <v>214</v>
-      </c>
-      <c r="AR15" t="s">
-        <v>215</v>
-      </c>
-      <c r="AS15" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
+        <v>213</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>213</v>
+      </c>
+      <c r="AS16" t="s">
         <v>214</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>214</v>
-      </c>
-      <c r="AS16" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="X17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AS17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AS18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:45" x14ac:dyDescent="0.2">
@@ -15186,110 +15198,110 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
+        <v>213</v>
+      </c>
+      <c r="H19" t="s">
+        <v>213</v>
+      </c>
+      <c r="J19" t="s">
         <v>214</v>
       </c>
-      <c r="H19" t="s">
+      <c r="K19" t="s">
         <v>214</v>
       </c>
-      <c r="J19" t="s">
-        <v>215</v>
-      </c>
-      <c r="K19" t="s">
-        <v>215</v>
-      </c>
       <c r="L19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P19" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q19" t="s">
         <v>214</v>
       </c>
-      <c r="Q19" t="s">
-        <v>215</v>
-      </c>
       <c r="AC19" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>213</v>
+      </c>
+      <c r="AE19" t="s">
         <v>214</v>
       </c>
-      <c r="AD19" t="s">
+      <c r="AG19" t="s">
+        <v>213</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>213</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>213</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>213</v>
+      </c>
+      <c r="AS19" t="s">
         <v>214</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>215</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>214</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>214</v>
-      </c>
-      <c r="AK19" t="s">
-        <v>214</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>214</v>
-      </c>
-      <c r="AQ19" t="s">
-        <v>214</v>
-      </c>
-      <c r="AS19" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AA20" t="s">
+        <v>213</v>
+      </c>
+      <c r="AS20" t="s">
         <v>214</v>
-      </c>
-      <c r="AS20" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="21" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AS21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X22" t="s">
+        <v>213</v>
+      </c>
+      <c r="AS22" t="s">
         <v>214</v>
-      </c>
-      <c r="AS22" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="S23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AJ23" t="s">
+        <v>213</v>
+      </c>
+      <c r="AS23" t="s">
         <v>214</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -15341,7 +15353,7 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -15459,13 +15471,13 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C25" s="5"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -15609,7 +15621,7 @@
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B13" s="36"/>
       <c r="C13" s="36"/>
@@ -15618,7 +15630,7 @@
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B14" s="36"/>
       <c r="C14" s="36"/>
@@ -15682,10 +15694,10 @@
         <v>12</v>
       </c>
       <c r="K16" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="L16" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="L16" s="10" t="s">
-        <v>219</v>
       </c>
       <c r="M16" s="10" t="s">
         <v>13</v>
@@ -15736,13 +15748,13 @@
         <v>80</v>
       </c>
       <c r="AC16" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="AD16" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="AE16" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="AD16" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="AE16" s="10" t="s">
-        <v>134</v>
       </c>
       <c r="AF16" s="10" t="s">
         <v>83</v>
@@ -15763,7 +15775,7 @@
         <v>85</v>
       </c>
       <c r="AL16" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AM16" s="10" t="s">
         <v>87</v>
@@ -15772,7 +15784,7 @@
         <v>22</v>
       </c>
       <c r="AO16" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AP16" s="10"/>
       <c r="AQ16" s="10"/>
@@ -17503,19 +17515,19 @@
   <sheetData>
     <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.2">
       <c r="A1" s="29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B1" s="29"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B2" s="31"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B3" s="31"/>
       <c r="G3" s="19" t="s">
@@ -17526,16 +17538,16 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>154</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>155</v>
       </c>
       <c r="E4" s="33" t="s">
         <v>3</v>
@@ -17761,103 +17773,124 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0F4C5A-BE41-6140-9B9B-80B8DB7D1AD7}">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" style="30" customWidth="1"/>
-    <col min="2" max="2" width="22" style="30" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" style="30" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="30" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" style="30" customWidth="1"/>
-    <col min="6" max="6" width="28.33203125" style="30" customWidth="1"/>
-    <col min="7" max="7" width="19" style="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16" style="30" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" style="30" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.5" style="30" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5" style="30" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.83203125" style="30" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.83203125" style="30" customWidth="1"/>
-    <col min="14" max="14" width="21.5" style="30" customWidth="1"/>
-    <col min="15" max="15" width="23" style="30" customWidth="1"/>
-    <col min="16" max="18" width="15.83203125" style="30" customWidth="1"/>
-    <col min="19" max="16384" width="8.83203125" style="30"/>
+    <col min="2" max="3" width="22" style="30" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" style="30" customWidth="1"/>
+    <col min="5" max="5" width="32.6640625" style="30" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="30" customWidth="1"/>
+    <col min="7" max="7" width="28.33203125" style="30" customWidth="1"/>
+    <col min="8" max="8" width="19" style="30" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="30" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.83203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5" style="30" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5" style="30" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.83203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.83203125" style="30" customWidth="1"/>
+    <col min="15" max="20" width="21.5" style="30" customWidth="1"/>
+    <col min="21" max="21" width="23" style="30" customWidth="1"/>
+    <col min="22" max="24" width="15.83203125" style="30" customWidth="1"/>
+    <col min="25" max="16384" width="8.83203125" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="24" x14ac:dyDescent="0.2">
       <c r="A1" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="B1" s="29"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
-        <v>138</v>
-      </c>
       <c r="B2" s="31"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C2" s="31"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="31"/>
       <c r="B3" s="31"/>
-      <c r="P3" s="19" t="s">
+      <c r="C3" s="31"/>
+      <c r="V3" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="W3" s="20"/>
+      <c r="X3" s="20"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="32" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="E4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="F4" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="J4" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="K4" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L4" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="M4" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="N4" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="O4" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="J4" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="K4" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="L4" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="M4" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="N4" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="O4" s="33" t="s">
+      <c r="P4" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q4" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="R4" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="S4" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="T4" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="U4" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="17"/>
       <c r="B5" s="17"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="17"/>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
@@ -17868,365 +17901,470 @@
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
       <c r="M5" s="15"/>
-      <c r="N5" s="17"/>
+      <c r="N5" s="15"/>
       <c r="O5" s="17"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="17"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
       <c r="M6" s="15"/>
-      <c r="N6" s="17"/>
+      <c r="N6" s="15"/>
       <c r="O6" s="17"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="15"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="17"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
-      <c r="N7" s="17"/>
+      <c r="N7" s="15"/>
       <c r="O7" s="17"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17"/>
+      <c r="V7" s="15"/>
+      <c r="W7" s="15"/>
+      <c r="X7" s="15"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="17"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
-      <c r="N8" s="17"/>
+      <c r="N8" s="15"/>
       <c r="O8" s="17"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="17"/>
+      <c r="V8" s="15"/>
+      <c r="W8" s="15"/>
+      <c r="X8" s="15"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="17"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="15"/>
+      <c r="C9" s="17"/>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
       <c r="J9" s="15"/>
       <c r="K9" s="15"/>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
-      <c r="N9" s="17"/>
+      <c r="N9" s="15"/>
       <c r="O9" s="17"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="15"/>
+      <c r="W9" s="15"/>
+      <c r="X9" s="15"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="17"/>
       <c r="B10" s="17"/>
-      <c r="C10" s="15"/>
+      <c r="C10" s="17"/>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
       <c r="K10" s="15"/>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
-      <c r="N10" s="17"/>
+      <c r="N10" s="15"/>
       <c r="O10" s="17"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="17"/>
       <c r="B11" s="17"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="17"/>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="27"/>
       <c r="H11" s="15"/>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
-      <c r="N11" s="17"/>
+      <c r="N11" s="15"/>
       <c r="O11" s="17"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="15"/>
+      <c r="W11" s="15"/>
+      <c r="X11" s="15"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="17"/>
       <c r="B12" s="17"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="17"/>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="27"/>
       <c r="H12" s="15"/>
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
-      <c r="N12" s="17"/>
+      <c r="N12" s="15"/>
       <c r="O12" s="17"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="15"/>
+      <c r="W12" s="15"/>
+      <c r="X12" s="15"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="17"/>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="27"/>
       <c r="H13" s="15"/>
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
-      <c r="N13" s="17"/>
+      <c r="N13" s="15"/>
       <c r="O13" s="17"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="15"/>
+      <c r="W13" s="15"/>
+      <c r="X13" s="15"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="17"/>
       <c r="B14" s="17"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="17"/>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="27"/>
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
-      <c r="N14" s="17"/>
+      <c r="N14" s="15"/>
       <c r="O14" s="17"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="17"/>
+      <c r="V14" s="15"/>
+      <c r="W14" s="15"/>
+      <c r="X14" s="15"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="17"/>
       <c r="B15" s="17"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="17"/>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="27"/>
       <c r="H15" s="15"/>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
-      <c r="N15" s="17"/>
+      <c r="N15" s="15"/>
       <c r="O15" s="17"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="17"/>
+      <c r="V15" s="15"/>
+      <c r="W15" s="15"/>
+      <c r="X15" s="15"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="17"/>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="27"/>
       <c r="H16" s="15"/>
       <c r="I16" s="15"/>
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
-      <c r="N16" s="17"/>
+      <c r="N16" s="15"/>
       <c r="O16" s="17"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="17"/>
+      <c r="V16" s="15"/>
+      <c r="W16" s="15"/>
+      <c r="X16" s="15"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="17"/>
       <c r="B17" s="17"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="17"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="27"/>
       <c r="H17" s="15"/>
       <c r="I17" s="15"/>
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="15"/>
       <c r="O17" s="17"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="17"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="15"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
-      <c r="C18" s="15"/>
+      <c r="C18" s="17"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="27"/>
       <c r="H18" s="15"/>
       <c r="I18" s="15"/>
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
-      <c r="N18" s="17"/>
+      <c r="N18" s="15"/>
       <c r="O18" s="17"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17"/>
+      <c r="V18" s="15"/>
+      <c r="W18" s="15"/>
+      <c r="X18" s="15"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="17"/>
       <c r="B19" s="17"/>
-      <c r="C19" s="15"/>
+      <c r="C19" s="17"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="27"/>
       <c r="H19" s="15"/>
       <c r="I19" s="15"/>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
       <c r="L19" s="15"/>
       <c r="M19" s="15"/>
-      <c r="N19" s="17"/>
+      <c r="N19" s="15"/>
       <c r="O19" s="17"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="15"/>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17"/>
+      <c r="V19" s="15"/>
+      <c r="W19" s="15"/>
+      <c r="X19" s="15"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
-      <c r="C20" s="15"/>
+      <c r="C20" s="17"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="27"/>
       <c r="H20" s="15"/>
       <c r="I20" s="15"/>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
-      <c r="N20" s="17"/>
+      <c r="N20" s="15"/>
       <c r="O20" s="17"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="15"/>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="15"/>
+      <c r="W20" s="15"/>
+      <c r="X20" s="15"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
-      <c r="C21" s="15"/>
+      <c r="C21" s="17"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="27"/>
       <c r="H21" s="15"/>
       <c r="I21" s="15"/>
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="17"/>
+      <c r="N21" s="15"/>
       <c r="O21" s="17"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="15"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
+      <c r="V21" s="15"/>
+      <c r="W21" s="15"/>
+      <c r="X21" s="15"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:E21">
+  <conditionalFormatting sqref="F5:F21">
     <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
-      <formula>C5="sql"</formula>
+      <formula>D5="sql"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F21">
+  <conditionalFormatting sqref="G5:G21">
     <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
-      <formula>C5="library"</formula>
+      <formula>D5="library"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
-    <dataValidation allowBlank="1" sqref="C22:G42 P5:R21" xr:uid="{E994B14B-32F5-D346-A2D5-4948CC9EA8C3}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Data Quality Type" prompt="Data quality rules support different levels/stages of data quality attributes:_x000a__x000a_Text: A human-readable text that describes the quality of the data._x000a_Library rules: A maintained library of commonly-used predefined quality attributes such as rowCount, unique" sqref="C4" xr:uid="{F5034942-1DBE-6649-8226-7716B942E17B}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Scheduler" prompt="Name of the scheduler that runs the quality check, such as cron, Airflow, or Github Action." sqref="L5:M21" xr:uid="{32CE7D0C-23F9-9242-8EB2-22364F11133E}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Severity" prompt="The severity of the data quality rule, such as error or warning." sqref="K5:K21" xr:uid="{0F4D661D-23D9-2540-B241-435A8E49610F}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Implementation" prompt="The data quality check in the engine's specific format." sqref="J5:J21" xr:uid="{00416CE8-FD1E-374C-B0CF-0FDCB1952802}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Engine" prompt="Required for custom DQ rule: name of the third-party engine being used. Any value is authorized here but common values are soda, greatExpectations, montecarlo, etc." sqref="I5:I21" xr:uid="{0459F568-8532-4048-9CA7-5708CD6DF179}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Threshold Value" prompt="The acutal value for the treshold operator._x000a_For mustBeBetween adn mustNotBeBetween, use [lowerBoundry, upperBoundy] syntax, e.g. [0, 100]." sqref="H5:H21" xr:uid="{E792E24E-6B57-A948-A026-4637119AD944}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Quality Operator" prompt="The comparation operator specifies the condition to validate the rule._x000a_Use it together with the threshold value, e.g. mustBe 0, or mustBeBetween [0,100]_x000a_This is applicable for quality type sql and some library rules." sqref="G5:G21" xr:uid="{15B1EE74-8A6D-3F49-A7EC-55C27203D116}">
+  <dataValidations count="16">
+    <dataValidation allowBlank="1" sqref="D22:H42 V5:X21" xr:uid="{E994B14B-32F5-D346-A2D5-4948CC9EA8C3}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Data Quality Type" prompt="Data quality rules support different levels/stages of data quality attributes:_x000a__x000a_Text: A human-readable text that describes the quality of the data._x000a_Library rules: A maintained library of commonly-used predefined quality attributes such as rowCount, unique" sqref="D4" xr:uid="{F5034942-1DBE-6649-8226-7716B942E17B}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Scheduler" prompt="Name of the scheduler that runs the quality check, such as cron, Airflow, or Github Action." sqref="M5:N21" xr:uid="{32CE7D0C-23F9-9242-8EB2-22364F11133E}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Severity" prompt="The severity of the data quality rule, such as error or warning." sqref="L5:L21" xr:uid="{0F4D661D-23D9-2540-B241-435A8E49610F}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Implementation" prompt="The data quality check in the engine's specific format." sqref="K5:K21" xr:uid="{00416CE8-FD1E-374C-B0CF-0FDCB1952802}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Engine" prompt="Required for custom DQ rule: name of the third-party engine being used. Any value is authorized here but common values are soda, greatExpectations, montecarlo, etc." sqref="J5:J21" xr:uid="{0459F568-8532-4048-9CA7-5708CD6DF179}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Threshold Value" prompt="The acutal value for the treshold operator._x000a_For mustBeBetween adn mustNotBeBetween, use [lowerBoundry, upperBoundy] syntax, e.g. [0, 100]." sqref="I5:I21" xr:uid="{E792E24E-6B57-A948-A026-4637119AD944}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Quality Operator" prompt="The comparation operator specifies the condition to validate the rule._x000a_Use it together with the threshold value, e.g. mustBe 0, or mustBeBetween [0,100]_x000a_This is applicable for quality type sql and some library rules." sqref="H5:H21" xr:uid="{15B1EE74-8A6D-3F49-A7EC-55C27203D116}">
       <formula1>"mustBe, mustNotBe, mustBeGreaterThan, mustBeGreaterOrEqualTo, mustBeLessThan, mustBeLessOrEqualTo, mustBeBetween, mustNotBeBetween"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Query" prompt="A single SQL query that returns either a numeric or boolean value for comparison. The query must be written in the SQL dialect specific to the provided server. " sqref="F5:F21" xr:uid="{21D55077-EE2C-364C-A32A-00F4CC049BEA}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Quality Metric" prompt="The expected or guaranteed data quality from a business perspective._x000a__x000a_Maps to quality.description" sqref="E5:E21" xr:uid="{FA04105D-EE78-664F-8C72-4098B271EC60}">
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Query" prompt="A single SQL query that returns either a numeric or boolean value for comparison. The query must be written in the SQL dialect specific to the provided server. " sqref="G5:G21" xr:uid="{21D55077-EE2C-364C-A32A-00F4CC049BEA}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Quality Metric" prompt="The expected or guaranteed data quality from a business perspective._x000a__x000a_Maps to quality.description" sqref="F5:F21" xr:uid="{FA04105D-EE78-664F-8C72-4098B271EC60}">
       <formula1>"nullValues,missingValues,invalidValues,duplicateValues,rowCount"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C5:C21" xr:uid="{664F88A2-7556-9B4E-A851-8889D6576B99}">
+    <dataValidation type="list" allowBlank="1" sqref="D5:D21" xr:uid="{664F88A2-7556-9B4E-A851-8889D6576B99}">
       <formula1>"text,library,sql,custom"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality" prompt="The expected or guaranteed data quality from a business perspective._x000a__x000a_Maps to quality.description" sqref="D5:D21" xr:uid="{C84C6FF8-FC8D-B848-AC69-3DB82C6CB871}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality" prompt="The expected or guaranteed data quality from a business perspective._x000a__x000a_Maps to quality.description" sqref="E5:E21" xr:uid="{C84C6FF8-FC8D-B848-AC69-3DB82C6CB871}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Schema" prompt="The schema name must match the name of the schema (table, ...) in the previous sheets." sqref="A4" xr:uid="{67CAE90D-676C-A44B-B965-361A399ACA9A}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Property" prompt="Optional: Leave empty, if this is a schema-level quality check._x000a_The property must match the property name in the schema._x000a_" sqref="B4" xr:uid="{F3E67713-E117-6E46-AEFE-6861F5933838}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Rule" prompt="The predefined data quality rule from the library._x000a_Only appliable if &quot;Quality Type&quot; is set to &quot;library&quot; or empty (which is library by default, if a rule is defined)" sqref="E4" xr:uid="{4E8AA24F-1E70-FF4C-81CC-D9A25B05246C}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Property" prompt="Optional: Leave empty, if this is a schema-level quality check._x000a_The property must match the property name in the schema._x000a_" sqref="B4:C4" xr:uid="{F3E67713-E117-6E46-AEFE-6861F5933838}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Rule" prompt="The predefined data quality rule from the library._x000a_Only appliable if &quot;Quality Type&quot; is set to &quot;library&quot; or empty (which is library by default, if a rule is defined)" sqref="F4" xr:uid="{4E8AA24F-1E70-FF4C-81CC-D9A25B05246C}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P5:P100" xr:uid="{881CD803-6A20-894A-A9FF-DE919EE9E89D}">
+      <formula1>"accuracy,completeness,conformity,consistency,coverage,timeliness,uniqueness"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -18529,7 +18667,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B4" s="5"/>
     </row>
@@ -18821,249 +18959,294 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B433535-9968-AF4C-822D-F1478F01E2E0}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.1640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="59.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="39.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="32.83203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="34.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="26.1640625" style="2" customWidth="1"/>
-    <col min="7" max="9" width="15.83203125" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.83203125" style="2"/>
+    <col min="1" max="1" width="18.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.1640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="59.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="39.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32.83203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="34.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="26.1640625" style="2" customWidth="1"/>
+    <col min="9" max="11" width="15.83203125" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="40" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I3" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G3" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
       <c r="I4" s="10"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
       <c r="I5" s="15"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
       <c r="I6" s="15"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="15"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
       <c r="I8" s="15"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
       <c r="I9" s="15"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
       <c r="I10" s="15"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
       <c r="I11" s="15"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
       <c r="I12" s="15"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
       <c r="I13" s="15"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
       <c r="I14" s="15"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
       <c r="I15" s="15"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
       <c r="I16" s="15"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
       <c r="I17" s="15"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
       <c r="I18" s="15"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
       <c r="I19" s="15"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
       <c r="I20" s="15"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
       <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="B5:E61 F5:I21" xr:uid="{87F0D0D6-8894-A64F-B36D-300F6FA120B5}"/>
+  <dataValidations count="2">
+    <dataValidation allowBlank="1" sqref="D5:G61 H5:K21" xr:uid="{87F0D0D6-8894-A64F-B36D-300F6FA120B5}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:A100" xr:uid="{839C8FC8-93D0-9A4F-BA53-98416339B650}">
+      <formula1>"Contract,Server"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19089,12 +19272,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -19102,7 +19285,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" s="26"/>
     </row>
@@ -19121,25 +19304,25 @@
         <v>1</v>
       </c>
       <c r="C6" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="F6" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>105</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>3</v>
       </c>
       <c r="H6" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="I6" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>22</v>

--- a/odcs-template-v3.2.xlsx
+++ b/odcs-template-v3.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakob/entropyData/open-data-contract-standard-excel-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1031AD6A-ED8F-9542-9505-273B1DC3029A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342FE4F4-9DE3-3540-BE91-7790BCC57F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
     <definedName name="price.priceUnit">Pricing!$B$6</definedName>
     <definedName name="quality">Quality!$A$4:$BF$300</definedName>
     <definedName name="relationships">Relationships!$A$4:$AZ$300</definedName>
-    <definedName name="roles" localSheetId="7">Roles!$C$4:$BB$1000</definedName>
+    <definedName name="roles" localSheetId="7">Roles!$A$4:$AZ$1000</definedName>
     <definedName name="schema.businessName" localSheetId="2">'Schema &lt;table_name&gt;'!$B$8</definedName>
     <definedName name="schema.context.instructions" localSheetId="2">'Schema &lt;table_name&gt;'!$B$13</definedName>
     <definedName name="schema.dataGranularityDescription" localSheetId="2">'Schema &lt;table_name&gt;'!$B$10</definedName>
@@ -1124,7 +1124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1227,7 +1227,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -18980,7 +18979,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="4" t="s">
         <v>248</v>
       </c>
     </row>

--- a/odcs-template-v3.2.xlsx
+++ b/odcs-template-v3.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakob/entropyData/open-data-contract-standard-excel-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342FE4F4-9DE3-3540-BE91-7790BCC57F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3875D753-AACC-B04A-B375-AAA28B30B143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,20 +39,21 @@
     <definedName name="apiVersion">Fundamentals!$C$5</definedName>
     <definedName name="authoritativeDefinitions">'Authoritative Definitions'!$A$4:$F$1000</definedName>
     <definedName name="constraints">Constraints!$A$4:$AZ$1000</definedName>
-    <definedName name="context.instructions">Fundamentals!$C$25</definedName>
-    <definedName name="CustomProperties">'Custom Properties'!$A$5:$G$21</definedName>
+    <definedName name="context.instructions">Fundamentals!$C$26</definedName>
+    <definedName name="contractCreatedTs">Fundamentals!$C$11</definedName>
+    <definedName name="CustomProperties">'Custom Properties'!$A$5:$H$21</definedName>
     <definedName name="datacontract_id">Fundamentals!$C$7</definedName>
-    <definedName name="dataProduct">Fundamentals!$C$15</definedName>
-    <definedName name="description.limitations">Fundamentals!$C$20</definedName>
-    <definedName name="description.purpose">Fundamentals!$C$19</definedName>
-    <definedName name="description.usage">Fundamentals!$C$21</definedName>
-    <definedName name="domain">Fundamentals!$C$14</definedName>
+    <definedName name="dataProduct">Fundamentals!$C$16</definedName>
+    <definedName name="description.limitations">Fundamentals!$C$21</definedName>
+    <definedName name="description.purpose">Fundamentals!$C$20</definedName>
+    <definedName name="description.usage">Fundamentals!$C$22</definedName>
+    <definedName name="domain">Fundamentals!$C$15</definedName>
     <definedName name="enum">Enums!$A$4:$AZ$1000</definedName>
     <definedName name="id">Fundamentals!$C$7</definedName>
     <definedName name="instructions.importUrl">Instructions!$B$24</definedName>
     <definedName name="kind">Fundamentals!$C$4</definedName>
     <definedName name="name">Fundamentals!$C$8</definedName>
-    <definedName name="owner">Fundamentals!$C$12</definedName>
+    <definedName name="owner">Fundamentals!$C$13</definedName>
     <definedName name="price.id">Pricing!$B$7</definedName>
     <definedName name="price.priceAmount">Pricing!$B$4</definedName>
     <definedName name="price.priceCurrency">Pricing!$B$5</definedName>
@@ -69,7 +70,7 @@
     <definedName name="schema.name" localSheetId="2">'Schema &lt;table_name&gt;'!$B$5</definedName>
     <definedName name="schema.physicalName" localSheetId="2">'Schema &lt;table_name&gt;'!$B$9</definedName>
     <definedName name="schema.physicalType" localSheetId="2">'Schema &lt;table_name&gt;'!$B$6</definedName>
-    <definedName name="schema.properties" localSheetId="2">'Schema &lt;table_name&gt;'!$A$16:$AO$984</definedName>
+    <definedName name="schema.properties" localSheetId="2">'Schema &lt;table_name&gt;'!$A$16:$AW$984</definedName>
     <definedName name="schema.tags" localSheetId="2">'Schema &lt;table_name&gt;'!$B$11</definedName>
     <definedName name="servers.account">Servers!$C$11</definedName>
     <definedName name="servers.catalog">Servers!$C$12</definedName>
@@ -104,13 +105,13 @@
     <definedName name="status">Fundamentals!$C$10</definedName>
     <definedName name="support">Support!$A$4:$AZ$1000</definedName>
     <definedName name="synonyms">Synonyms!$A$4:$AZ$1000</definedName>
-    <definedName name="tags">Fundamentals!$C$23</definedName>
-    <definedName name="team">Team!$A$10:$AZ$1006</definedName>
+    <definedName name="tags">Fundamentals!$C$24</definedName>
+    <definedName name="team">Team!$A$10:$BA$1006</definedName>
     <definedName name="team.description">Team!$B$5</definedName>
     <definedName name="team.id">Team!$B$7</definedName>
     <definedName name="team.name">Team!$B$4</definedName>
     <definedName name="team.tags">Team!$B$6</definedName>
-    <definedName name="tenant">Fundamentals!$C$16</definedName>
+    <definedName name="tenant">Fundamentals!$C$17</definedName>
     <definedName name="verifiedStatements">'Verified Statements'!$A$4:$AZ$1000</definedName>
     <definedName name="version">Fundamentals!$C$9</definedName>
   </definedNames>
@@ -132,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="260">
   <si>
     <t>Property</t>
   </si>
@@ -905,6 +906,39 @@
   <si>
     <t xml:space="preserve">This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
 </t>
+  </si>
+  <si>
+    <t>Dimensions</t>
+  </si>
+  <si>
+    <t>Element Type</t>
+  </si>
+  <si>
+    <t>Distance Metric</t>
+  </si>
+  <si>
+    <t>Normalized</t>
+  </si>
+  <si>
+    <t>Embedding Model</t>
+  </si>
+  <si>
+    <t>Embedding Model Version</t>
+  </si>
+  <si>
+    <t>Value Type</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Contract Created</t>
+  </si>
+  <si>
+    <t>Timezone</t>
+  </si>
+  <si>
+    <t>Default Timezone</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1208,6 +1242,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -14328,35 +14365,36 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29635FC6-19E5-6E43-84D3-3161FAC792B3}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="22.5" style="2" customWidth="1"/>
     <col min="3" max="3" width="33.1640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="43.1640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="36.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="28.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.83203125" style="2"/>
+    <col min="5" max="5" width="11.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="30" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>55</v>
       </c>
@@ -14370,16 +14408,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">
@@ -14389,159 +14430,213 @@
         <f>IF(owner &lt;&gt; "", owner, "")</f>
         <v/>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+      <c r="E7" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
+      <c r="E8" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
+      <c r="E9" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
+      <c r="E10" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
+      <c r="E12" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
+      <c r="E13" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+      <c r="E16" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
+      <c r="E18" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
+      <c r="E19" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
+      <c r="E20" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
+      <c r="E21" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation allowBlank="1" sqref="D5:D61 E5:G21 B5:B22" xr:uid="{39D00745-E29F-BB4D-8EFF-9275524C1814}"/>
+  <dataValidations count="3">
+    <dataValidation allowBlank="1" sqref="B5:B22 F5:H21 D5:D61" xr:uid="{39D00745-E29F-BB4D-8EFF-9275524C1814}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:A100" xr:uid="{9046F39E-9EB3-EF47-83AF-F83388AB159D}">
       <formula1>"Contract,Description,Server,Schema,Property,Enum Value,Synonym,Relationship,Quality,Support,Team,Team Member,Role,SLA,Verified Statement,Constraint"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E5:E100" xr:uid="{FD2B148B-B740-B14F-B337-F0CE13B025AB}">
+      <formula1>"Text,JSON"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15310,7 +15405,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92ABE851-FB8B-2145-B7F8-5CF6722D55A6}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.83203125" style="2" customWidth="1"/>
@@ -15388,32 +15483,31 @@
       <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="7"/>
+      <c r="A11" s="7" t="s">
+        <v>257</v>
+      </c>
       <c r="B11" s="7"/>
+      <c r="C11" s="34"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="5"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="5"/>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="A14" s="7"/>
       <c r="B14" s="7"/>
-      <c r="C14" s="5"/>
-      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="5"/>
@@ -15421,77 +15515,85 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="5"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
+      <c r="A17" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="B17" s="7"/>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="7"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="5"/>
+      <c r="B19" s="7"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" s="5"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21" s="5"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
+      <c r="B22" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="5"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="5"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
+      <c r="B24" s="7"/>
+      <c r="C24" s="5"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="C25" s="5"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B26" s="2" t="s">
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B27" s="2" t="s">
         <v>241</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="G11:L13 G17:L24" xr:uid="{7EB39568-B879-514E-B51D-6C44C6D6A95F}">
+    <dataValidation type="list" allowBlank="1" sqref="G12:L14 G18:L25" xr:uid="{7EB39568-B879-514E-B51D-6C44C6D6A95F}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D22 D17:D18 D11:D13 D24" xr:uid="{1D2456BD-0546-F940-A9EF-51615EED43D0}">
+    <dataValidation type="list" allowBlank="1" sqref="D23 D18:D19 D12:D14 D25" xr:uid="{1D2456BD-0546-F940-A9EF-51615EED43D0}">
       <formula1>"string,number,integer,boolean,array,object"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Owner" prompt="The ID of the team owning the Data Contract._x000a_Required for Data Mesh Manager." sqref="C12" xr:uid="{35986E89-F1AF-D84C-96AD-8E5AC4A64A86}"/>
-    <dataValidation allowBlank="1" sqref="C11:C13 C17:C18 C22:C65" xr:uid="{D875F021-2666-244F-B1D7-40151775E3CC}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Owner" prompt="The ID of the team owning the Data Contract._x000a_Required for Data Mesh Manager." sqref="C13" xr:uid="{35986E89-F1AF-D84C-96AD-8E5AC4A64A86}"/>
+    <dataValidation allowBlank="1" sqref="C12:C14 C18:C19 C23:C66" xr:uid="{D875F021-2666-244F-B1D7-40151775E3CC}"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -15500,7 +15602,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AR52"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.83203125" style="2" customWidth="1"/>
@@ -15521,122 +15623,122 @@
     <col min="18" max="22" width="19" style="2" customWidth="1"/>
     <col min="23" max="23" width="21.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="27.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="40" width="15.5" style="2" customWidth="1"/>
-    <col min="41" max="41" width="44.33203125" style="2" customWidth="1"/>
-    <col min="42" max="44" width="15.83203125" style="2" customWidth="1"/>
-    <col min="45" max="16384" width="8.83203125" style="2"/>
+    <col min="25" max="48" width="15.5" style="2" customWidth="1"/>
+    <col min="49" max="49" width="44.33203125" style="2" customWidth="1"/>
+    <col min="50" max="52" width="15.83203125" style="2" customWidth="1"/>
+    <col min="53" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:52" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-    </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-    </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="39"/>
-    </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="B8" s="38"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="40"/>
+    </row>
+    <row r="9" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="39"/>
-    </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="B9" s="38"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="40"/>
+    </row>
+    <row r="10" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="37"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="39"/>
-    </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="B10" s="38"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="40"/>
+    </row>
+    <row r="11" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-    </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+    </row>
+    <row r="12" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-    </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+    </row>
+    <row r="13" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-    </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+    </row>
+    <row r="14" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-    </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+    </row>
+    <row r="15" spans="1:52" x14ac:dyDescent="0.2">
       <c r="E15" s="2"/>
       <c r="Y15" s="19" t="s">
         <v>77</v>
@@ -15654,14 +15756,22 @@
       <c r="AJ15" s="20"/>
       <c r="AK15" s="20"/>
       <c r="AL15" s="20"/>
-      <c r="AM15" s="21"/>
-      <c r="AP15" s="19" t="s">
-        <v>31</v>
-      </c>
+      <c r="AM15" s="20"/>
+      <c r="AN15" s="20"/>
+      <c r="AO15" s="20"/>
+      <c r="AP15" s="20"/>
       <c r="AQ15" s="20"/>
       <c r="AR15" s="20"/>
-    </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS15" s="20"/>
+      <c r="AT15" s="20"/>
+      <c r="AU15" s="21"/>
+      <c r="AX15" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AY15" s="20"/>
+      <c r="AZ15" s="20"/>
+    </row>
+    <row r="16" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
         <v>0</v>
       </c>
@@ -15780,16 +15890,40 @@
         <v>87</v>
       </c>
       <c r="AN16" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="AO16" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="AP16" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="AQ16" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="AR16" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="AS16" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="AT16" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="AU16" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="AV16" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="AO16" s="10" t="s">
+      <c r="AW16" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="AP16" s="10"/>
-      <c r="AQ16" s="10"/>
-      <c r="AR16" s="10"/>
-    </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AX16" s="10"/>
+      <c r="AY16" s="10"/>
+      <c r="AZ16" s="10"/>
+    </row>
+    <row r="17" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A17" s="17"/>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
@@ -15820,22 +15954,30 @@
       <c r="AB17" s="15"/>
       <c r="AC17" s="15"/>
       <c r="AD17" s="15"/>
-      <c r="AE17" s="15"/>
-      <c r="AF17" s="15"/>
-      <c r="AG17" s="15"/>
-      <c r="AH17" s="15"/>
+      <c r="AE17" s="16"/>
+      <c r="AF17" s="16"/>
+      <c r="AG17" s="16"/>
+      <c r="AH17" s="16"/>
       <c r="AI17" s="15"/>
       <c r="AJ17" s="15"/>
       <c r="AK17" s="15"/>
       <c r="AL17" s="15"/>
       <c r="AM17" s="15"/>
       <c r="AN17" s="15"/>
-      <c r="AO17" s="28"/>
+      <c r="AO17" s="15"/>
       <c r="AP17" s="15"/>
       <c r="AQ17" s="15"/>
       <c r="AR17" s="15"/>
-    </row>
-    <row r="18" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS17" s="15"/>
+      <c r="AT17" s="15"/>
+      <c r="AU17" s="15"/>
+      <c r="AV17" s="15"/>
+      <c r="AW17" s="28"/>
+      <c r="AX17" s="15"/>
+      <c r="AY17" s="15"/>
+      <c r="AZ17" s="15"/>
+    </row>
+    <row r="18" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A18" s="17"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -15866,22 +16008,30 @@
       <c r="AB18" s="15"/>
       <c r="AC18" s="15"/>
       <c r="AD18" s="15"/>
-      <c r="AE18" s="15"/>
-      <c r="AF18" s="15"/>
-      <c r="AG18" s="15"/>
-      <c r="AH18" s="15"/>
+      <c r="AE18" s="16"/>
+      <c r="AF18" s="16"/>
+      <c r="AG18" s="16"/>
+      <c r="AH18" s="16"/>
       <c r="AI18" s="15"/>
       <c r="AJ18" s="15"/>
       <c r="AK18" s="15"/>
       <c r="AL18" s="15"/>
       <c r="AM18" s="15"/>
       <c r="AN18" s="15"/>
-      <c r="AO18" s="28"/>
+      <c r="AO18" s="15"/>
       <c r="AP18" s="15"/>
       <c r="AQ18" s="15"/>
       <c r="AR18" s="15"/>
-    </row>
-    <row r="19" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS18" s="15"/>
+      <c r="AT18" s="15"/>
+      <c r="AU18" s="15"/>
+      <c r="AV18" s="15"/>
+      <c r="AW18" s="28"/>
+      <c r="AX18" s="15"/>
+      <c r="AY18" s="15"/>
+      <c r="AZ18" s="15"/>
+    </row>
+    <row r="19" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A19" s="17"/>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -15912,22 +16062,30 @@
       <c r="AB19" s="15"/>
       <c r="AC19" s="15"/>
       <c r="AD19" s="15"/>
-      <c r="AE19" s="15"/>
-      <c r="AF19" s="15"/>
-      <c r="AG19" s="15"/>
-      <c r="AH19" s="15"/>
+      <c r="AE19" s="16"/>
+      <c r="AF19" s="16"/>
+      <c r="AG19" s="16"/>
+      <c r="AH19" s="16"/>
       <c r="AI19" s="15"/>
       <c r="AJ19" s="15"/>
       <c r="AK19" s="15"/>
       <c r="AL19" s="15"/>
       <c r="AM19" s="15"/>
       <c r="AN19" s="15"/>
-      <c r="AO19" s="28"/>
+      <c r="AO19" s="15"/>
       <c r="AP19" s="15"/>
       <c r="AQ19" s="15"/>
       <c r="AR19" s="15"/>
-    </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS19" s="15"/>
+      <c r="AT19" s="15"/>
+      <c r="AU19" s="15"/>
+      <c r="AV19" s="15"/>
+      <c r="AW19" s="28"/>
+      <c r="AX19" s="15"/>
+      <c r="AY19" s="15"/>
+      <c r="AZ19" s="15"/>
+    </row>
+    <row r="20" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A20" s="17"/>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -15958,22 +16116,30 @@
       <c r="AB20" s="15"/>
       <c r="AC20" s="15"/>
       <c r="AD20" s="15"/>
-      <c r="AE20" s="15"/>
-      <c r="AF20" s="15"/>
-      <c r="AG20" s="15"/>
-      <c r="AH20" s="15"/>
+      <c r="AE20" s="16"/>
+      <c r="AF20" s="16"/>
+      <c r="AG20" s="16"/>
+      <c r="AH20" s="16"/>
       <c r="AI20" s="15"/>
       <c r="AJ20" s="15"/>
       <c r="AK20" s="15"/>
       <c r="AL20" s="15"/>
       <c r="AM20" s="15"/>
       <c r="AN20" s="15"/>
-      <c r="AO20" s="28"/>
+      <c r="AO20" s="15"/>
       <c r="AP20" s="15"/>
       <c r="AQ20" s="15"/>
       <c r="AR20" s="15"/>
-    </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS20" s="15"/>
+      <c r="AT20" s="15"/>
+      <c r="AU20" s="15"/>
+      <c r="AV20" s="15"/>
+      <c r="AW20" s="28"/>
+      <c r="AX20" s="15"/>
+      <c r="AY20" s="15"/>
+      <c r="AZ20" s="15"/>
+    </row>
+    <row r="21" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A21" s="17"/>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -16004,22 +16170,30 @@
       <c r="AB21" s="15"/>
       <c r="AC21" s="15"/>
       <c r="AD21" s="15"/>
-      <c r="AE21" s="15"/>
-      <c r="AF21" s="15"/>
-      <c r="AG21" s="15"/>
-      <c r="AH21" s="15"/>
+      <c r="AE21" s="16"/>
+      <c r="AF21" s="16"/>
+      <c r="AG21" s="16"/>
+      <c r="AH21" s="16"/>
       <c r="AI21" s="15"/>
       <c r="AJ21" s="15"/>
       <c r="AK21" s="15"/>
       <c r="AL21" s="15"/>
       <c r="AM21" s="15"/>
       <c r="AN21" s="15"/>
-      <c r="AO21" s="28"/>
+      <c r="AO21" s="15"/>
       <c r="AP21" s="15"/>
       <c r="AQ21" s="15"/>
       <c r="AR21" s="15"/>
-    </row>
-    <row r="22" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS21" s="15"/>
+      <c r="AT21" s="15"/>
+      <c r="AU21" s="15"/>
+      <c r="AV21" s="15"/>
+      <c r="AW21" s="28"/>
+      <c r="AX21" s="15"/>
+      <c r="AY21" s="15"/>
+      <c r="AZ21" s="15"/>
+    </row>
+    <row r="22" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A22" s="17"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -16050,22 +16224,30 @@
       <c r="AB22" s="15"/>
       <c r="AC22" s="15"/>
       <c r="AD22" s="15"/>
-      <c r="AE22" s="15"/>
-      <c r="AF22" s="15"/>
-      <c r="AG22" s="15"/>
-      <c r="AH22" s="15"/>
+      <c r="AE22" s="16"/>
+      <c r="AF22" s="16"/>
+      <c r="AG22" s="16"/>
+      <c r="AH22" s="16"/>
       <c r="AI22" s="15"/>
       <c r="AJ22" s="15"/>
       <c r="AK22" s="15"/>
       <c r="AL22" s="15"/>
       <c r="AM22" s="15"/>
       <c r="AN22" s="15"/>
-      <c r="AO22" s="28"/>
+      <c r="AO22" s="15"/>
       <c r="AP22" s="15"/>
       <c r="AQ22" s="15"/>
       <c r="AR22" s="15"/>
-    </row>
-    <row r="23" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS22" s="15"/>
+      <c r="AT22" s="15"/>
+      <c r="AU22" s="15"/>
+      <c r="AV22" s="15"/>
+      <c r="AW22" s="28"/>
+      <c r="AX22" s="15"/>
+      <c r="AY22" s="15"/>
+      <c r="AZ22" s="15"/>
+    </row>
+    <row r="23" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A23" s="17"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -16096,22 +16278,30 @@
       <c r="AB23" s="15"/>
       <c r="AC23" s="15"/>
       <c r="AD23" s="15"/>
-      <c r="AE23" s="15"/>
-      <c r="AF23" s="15"/>
-      <c r="AG23" s="15"/>
-      <c r="AH23" s="15"/>
+      <c r="AE23" s="16"/>
+      <c r="AF23" s="16"/>
+      <c r="AG23" s="16"/>
+      <c r="AH23" s="16"/>
       <c r="AI23" s="15"/>
       <c r="AJ23" s="15"/>
       <c r="AK23" s="15"/>
       <c r="AL23" s="15"/>
       <c r="AM23" s="15"/>
       <c r="AN23" s="15"/>
-      <c r="AO23" s="28"/>
+      <c r="AO23" s="15"/>
       <c r="AP23" s="15"/>
       <c r="AQ23" s="15"/>
       <c r="AR23" s="15"/>
-    </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS23" s="15"/>
+      <c r="AT23" s="15"/>
+      <c r="AU23" s="15"/>
+      <c r="AV23" s="15"/>
+      <c r="AW23" s="28"/>
+      <c r="AX23" s="15"/>
+      <c r="AY23" s="15"/>
+      <c r="AZ23" s="15"/>
+    </row>
+    <row r="24" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A24" s="18"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -16142,22 +16332,30 @@
       <c r="AB24" s="15"/>
       <c r="AC24" s="15"/>
       <c r="AD24" s="15"/>
-      <c r="AE24" s="15"/>
-      <c r="AF24" s="15"/>
-      <c r="AG24" s="15"/>
-      <c r="AH24" s="15"/>
+      <c r="AE24" s="16"/>
+      <c r="AF24" s="16"/>
+      <c r="AG24" s="16"/>
+      <c r="AH24" s="16"/>
       <c r="AI24" s="15"/>
       <c r="AJ24" s="15"/>
       <c r="AK24" s="15"/>
       <c r="AL24" s="15"/>
       <c r="AM24" s="15"/>
       <c r="AN24" s="15"/>
-      <c r="AO24" s="28"/>
+      <c r="AO24" s="15"/>
       <c r="AP24" s="15"/>
       <c r="AQ24" s="15"/>
       <c r="AR24" s="15"/>
-    </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS24" s="15"/>
+      <c r="AT24" s="15"/>
+      <c r="AU24" s="15"/>
+      <c r="AV24" s="15"/>
+      <c r="AW24" s="28"/>
+      <c r="AX24" s="15"/>
+      <c r="AY24" s="15"/>
+      <c r="AZ24" s="15"/>
+    </row>
+    <row r="25" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A25" s="18"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -16188,22 +16386,30 @@
       <c r="AB25" s="15"/>
       <c r="AC25" s="15"/>
       <c r="AD25" s="15"/>
-      <c r="AE25" s="15"/>
-      <c r="AF25" s="15"/>
-      <c r="AG25" s="15"/>
-      <c r="AH25" s="15"/>
+      <c r="AE25" s="16"/>
+      <c r="AF25" s="16"/>
+      <c r="AG25" s="16"/>
+      <c r="AH25" s="16"/>
       <c r="AI25" s="15"/>
       <c r="AJ25" s="15"/>
       <c r="AK25" s="15"/>
       <c r="AL25" s="15"/>
       <c r="AM25" s="15"/>
       <c r="AN25" s="15"/>
-      <c r="AO25" s="28"/>
+      <c r="AO25" s="15"/>
       <c r="AP25" s="15"/>
       <c r="AQ25" s="15"/>
       <c r="AR25" s="15"/>
-    </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS25" s="15"/>
+      <c r="AT25" s="15"/>
+      <c r="AU25" s="15"/>
+      <c r="AV25" s="15"/>
+      <c r="AW25" s="28"/>
+      <c r="AX25" s="15"/>
+      <c r="AY25" s="15"/>
+      <c r="AZ25" s="15"/>
+    </row>
+    <row r="26" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A26" s="18"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -16234,22 +16440,30 @@
       <c r="AB26" s="15"/>
       <c r="AC26" s="15"/>
       <c r="AD26" s="15"/>
-      <c r="AE26" s="15"/>
-      <c r="AF26" s="15"/>
-      <c r="AG26" s="15"/>
-      <c r="AH26" s="15"/>
+      <c r="AE26" s="16"/>
+      <c r="AF26" s="16"/>
+      <c r="AG26" s="16"/>
+      <c r="AH26" s="16"/>
       <c r="AI26" s="15"/>
       <c r="AJ26" s="15"/>
       <c r="AK26" s="15"/>
       <c r="AL26" s="15"/>
       <c r="AM26" s="15"/>
       <c r="AN26" s="15"/>
-      <c r="AO26" s="28"/>
+      <c r="AO26" s="15"/>
       <c r="AP26" s="15"/>
       <c r="AQ26" s="15"/>
       <c r="AR26" s="15"/>
-    </row>
-    <row r="27" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS26" s="15"/>
+      <c r="AT26" s="15"/>
+      <c r="AU26" s="15"/>
+      <c r="AV26" s="15"/>
+      <c r="AW26" s="28"/>
+      <c r="AX26" s="15"/>
+      <c r="AY26" s="15"/>
+      <c r="AZ26" s="15"/>
+    </row>
+    <row r="27" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A27" s="17"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -16280,22 +16494,30 @@
       <c r="AB27" s="15"/>
       <c r="AC27" s="15"/>
       <c r="AD27" s="15"/>
-      <c r="AE27" s="15"/>
-      <c r="AF27" s="15"/>
-      <c r="AG27" s="15"/>
-      <c r="AH27" s="15"/>
+      <c r="AE27" s="16"/>
+      <c r="AF27" s="16"/>
+      <c r="AG27" s="16"/>
+      <c r="AH27" s="16"/>
       <c r="AI27" s="15"/>
       <c r="AJ27" s="15"/>
       <c r="AK27" s="15"/>
       <c r="AL27" s="15"/>
       <c r="AM27" s="15"/>
       <c r="AN27" s="15"/>
-      <c r="AO27" s="28"/>
+      <c r="AO27" s="15"/>
       <c r="AP27" s="15"/>
       <c r="AQ27" s="15"/>
       <c r="AR27" s="15"/>
-    </row>
-    <row r="28" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS27" s="15"/>
+      <c r="AT27" s="15"/>
+      <c r="AU27" s="15"/>
+      <c r="AV27" s="15"/>
+      <c r="AW27" s="28"/>
+      <c r="AX27" s="15"/>
+      <c r="AY27" s="15"/>
+      <c r="AZ27" s="15"/>
+    </row>
+    <row r="28" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A28" s="17"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -16326,22 +16548,30 @@
       <c r="AB28" s="15"/>
       <c r="AC28" s="15"/>
       <c r="AD28" s="15"/>
-      <c r="AE28" s="15"/>
-      <c r="AF28" s="15"/>
-      <c r="AG28" s="15"/>
-      <c r="AH28" s="15"/>
+      <c r="AE28" s="16"/>
+      <c r="AF28" s="16"/>
+      <c r="AG28" s="16"/>
+      <c r="AH28" s="16"/>
       <c r="AI28" s="15"/>
       <c r="AJ28" s="15"/>
       <c r="AK28" s="15"/>
       <c r="AL28" s="15"/>
       <c r="AM28" s="15"/>
       <c r="AN28" s="15"/>
-      <c r="AO28" s="28"/>
+      <c r="AO28" s="15"/>
       <c r="AP28" s="15"/>
       <c r="AQ28" s="15"/>
       <c r="AR28" s="15"/>
-    </row>
-    <row r="29" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS28" s="15"/>
+      <c r="AT28" s="15"/>
+      <c r="AU28" s="15"/>
+      <c r="AV28" s="15"/>
+      <c r="AW28" s="28"/>
+      <c r="AX28" s="15"/>
+      <c r="AY28" s="15"/>
+      <c r="AZ28" s="15"/>
+    </row>
+    <row r="29" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A29" s="17"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -16372,22 +16602,30 @@
       <c r="AB29" s="15"/>
       <c r="AC29" s="15"/>
       <c r="AD29" s="15"/>
-      <c r="AE29" s="15"/>
-      <c r="AF29" s="15"/>
-      <c r="AG29" s="15"/>
-      <c r="AH29" s="15"/>
+      <c r="AE29" s="16"/>
+      <c r="AF29" s="16"/>
+      <c r="AG29" s="16"/>
+      <c r="AH29" s="16"/>
       <c r="AI29" s="15"/>
       <c r="AJ29" s="15"/>
       <c r="AK29" s="15"/>
       <c r="AL29" s="15"/>
       <c r="AM29" s="15"/>
       <c r="AN29" s="15"/>
-      <c r="AO29" s="28"/>
+      <c r="AO29" s="15"/>
       <c r="AP29" s="15"/>
       <c r="AQ29" s="15"/>
       <c r="AR29" s="15"/>
-    </row>
-    <row r="30" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS29" s="15"/>
+      <c r="AT29" s="15"/>
+      <c r="AU29" s="15"/>
+      <c r="AV29" s="15"/>
+      <c r="AW29" s="28"/>
+      <c r="AX29" s="15"/>
+      <c r="AY29" s="15"/>
+      <c r="AZ29" s="15"/>
+    </row>
+    <row r="30" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A30" s="17"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -16418,22 +16656,30 @@
       <c r="AB30" s="15"/>
       <c r="AC30" s="15"/>
       <c r="AD30" s="15"/>
-      <c r="AE30" s="15"/>
-      <c r="AF30" s="15"/>
-      <c r="AG30" s="15"/>
-      <c r="AH30" s="15"/>
+      <c r="AE30" s="16"/>
+      <c r="AF30" s="16"/>
+      <c r="AG30" s="16"/>
+      <c r="AH30" s="16"/>
       <c r="AI30" s="15"/>
       <c r="AJ30" s="15"/>
       <c r="AK30" s="15"/>
       <c r="AL30" s="15"/>
       <c r="AM30" s="15"/>
       <c r="AN30" s="15"/>
-      <c r="AO30" s="28"/>
+      <c r="AO30" s="15"/>
       <c r="AP30" s="15"/>
       <c r="AQ30" s="15"/>
       <c r="AR30" s="15"/>
-    </row>
-    <row r="31" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS30" s="15"/>
+      <c r="AT30" s="15"/>
+      <c r="AU30" s="15"/>
+      <c r="AV30" s="15"/>
+      <c r="AW30" s="28"/>
+      <c r="AX30" s="15"/>
+      <c r="AY30" s="15"/>
+      <c r="AZ30" s="15"/>
+    </row>
+    <row r="31" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A31" s="17"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -16464,22 +16710,30 @@
       <c r="AB31" s="15"/>
       <c r="AC31" s="15"/>
       <c r="AD31" s="15"/>
-      <c r="AE31" s="15"/>
-      <c r="AF31" s="15"/>
-      <c r="AG31" s="15"/>
-      <c r="AH31" s="15"/>
+      <c r="AE31" s="16"/>
+      <c r="AF31" s="16"/>
+      <c r="AG31" s="16"/>
+      <c r="AH31" s="16"/>
       <c r="AI31" s="15"/>
       <c r="AJ31" s="15"/>
       <c r="AK31" s="15"/>
       <c r="AL31" s="15"/>
       <c r="AM31" s="15"/>
       <c r="AN31" s="15"/>
-      <c r="AO31" s="28"/>
+      <c r="AO31" s="15"/>
       <c r="AP31" s="15"/>
       <c r="AQ31" s="15"/>
       <c r="AR31" s="15"/>
-    </row>
-    <row r="32" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS31" s="15"/>
+      <c r="AT31" s="15"/>
+      <c r="AU31" s="15"/>
+      <c r="AV31" s="15"/>
+      <c r="AW31" s="28"/>
+      <c r="AX31" s="15"/>
+      <c r="AY31" s="15"/>
+      <c r="AZ31" s="15"/>
+    </row>
+    <row r="32" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A32" s="17"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -16510,22 +16764,30 @@
       <c r="AB32" s="15"/>
       <c r="AC32" s="15"/>
       <c r="AD32" s="15"/>
-      <c r="AE32" s="15"/>
-      <c r="AF32" s="15"/>
-      <c r="AG32" s="15"/>
-      <c r="AH32" s="15"/>
+      <c r="AE32" s="16"/>
+      <c r="AF32" s="16"/>
+      <c r="AG32" s="16"/>
+      <c r="AH32" s="16"/>
       <c r="AI32" s="15"/>
       <c r="AJ32" s="15"/>
       <c r="AK32" s="15"/>
       <c r="AL32" s="15"/>
       <c r="AM32" s="15"/>
       <c r="AN32" s="15"/>
-      <c r="AO32" s="28"/>
+      <c r="AO32" s="15"/>
       <c r="AP32" s="15"/>
       <c r="AQ32" s="15"/>
       <c r="AR32" s="15"/>
-    </row>
-    <row r="33" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS32" s="15"/>
+      <c r="AT32" s="15"/>
+      <c r="AU32" s="15"/>
+      <c r="AV32" s="15"/>
+      <c r="AW32" s="28"/>
+      <c r="AX32" s="15"/>
+      <c r="AY32" s="15"/>
+      <c r="AZ32" s="15"/>
+    </row>
+    <row r="33" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A33" s="17"/>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -16556,22 +16818,30 @@
       <c r="AB33" s="15"/>
       <c r="AC33" s="15"/>
       <c r="AD33" s="15"/>
-      <c r="AE33" s="15"/>
-      <c r="AF33" s="15"/>
-      <c r="AG33" s="15"/>
-      <c r="AH33" s="15"/>
+      <c r="AE33" s="16"/>
+      <c r="AF33" s="16"/>
+      <c r="AG33" s="16"/>
+      <c r="AH33" s="16"/>
       <c r="AI33" s="15"/>
       <c r="AJ33" s="15"/>
       <c r="AK33" s="15"/>
       <c r="AL33" s="15"/>
       <c r="AM33" s="15"/>
       <c r="AN33" s="15"/>
-      <c r="AO33" s="28"/>
+      <c r="AO33" s="15"/>
       <c r="AP33" s="15"/>
       <c r="AQ33" s="15"/>
       <c r="AR33" s="15"/>
-    </row>
-    <row r="34" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS33" s="15"/>
+      <c r="AT33" s="15"/>
+      <c r="AU33" s="15"/>
+      <c r="AV33" s="15"/>
+      <c r="AW33" s="28"/>
+      <c r="AX33" s="15"/>
+      <c r="AY33" s="15"/>
+      <c r="AZ33" s="15"/>
+    </row>
+    <row r="34" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A34" s="17"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -16602,22 +16872,30 @@
       <c r="AB34" s="15"/>
       <c r="AC34" s="15"/>
       <c r="AD34" s="15"/>
-      <c r="AE34" s="15"/>
-      <c r="AF34" s="15"/>
-      <c r="AG34" s="15"/>
-      <c r="AH34" s="15"/>
+      <c r="AE34" s="16"/>
+      <c r="AF34" s="16"/>
+      <c r="AG34" s="16"/>
+      <c r="AH34" s="16"/>
       <c r="AI34" s="15"/>
       <c r="AJ34" s="15"/>
       <c r="AK34" s="15"/>
       <c r="AL34" s="15"/>
       <c r="AM34" s="15"/>
       <c r="AN34" s="15"/>
-      <c r="AO34" s="28"/>
+      <c r="AO34" s="15"/>
       <c r="AP34" s="15"/>
       <c r="AQ34" s="15"/>
       <c r="AR34" s="15"/>
-    </row>
-    <row r="35" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS34" s="15"/>
+      <c r="AT34" s="15"/>
+      <c r="AU34" s="15"/>
+      <c r="AV34" s="15"/>
+      <c r="AW34" s="28"/>
+      <c r="AX34" s="15"/>
+      <c r="AY34" s="15"/>
+      <c r="AZ34" s="15"/>
+    </row>
+    <row r="35" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A35" s="17"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -16648,22 +16926,30 @@
       <c r="AB35" s="15"/>
       <c r="AC35" s="15"/>
       <c r="AD35" s="15"/>
-      <c r="AE35" s="15"/>
-      <c r="AF35" s="15"/>
-      <c r="AG35" s="15"/>
-      <c r="AH35" s="15"/>
+      <c r="AE35" s="16"/>
+      <c r="AF35" s="16"/>
+      <c r="AG35" s="16"/>
+      <c r="AH35" s="16"/>
       <c r="AI35" s="15"/>
       <c r="AJ35" s="15"/>
       <c r="AK35" s="15"/>
       <c r="AL35" s="15"/>
       <c r="AM35" s="15"/>
       <c r="AN35" s="15"/>
-      <c r="AO35" s="28"/>
+      <c r="AO35" s="15"/>
       <c r="AP35" s="15"/>
       <c r="AQ35" s="15"/>
       <c r="AR35" s="15"/>
-    </row>
-    <row r="36" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS35" s="15"/>
+      <c r="AT35" s="15"/>
+      <c r="AU35" s="15"/>
+      <c r="AV35" s="15"/>
+      <c r="AW35" s="28"/>
+      <c r="AX35" s="15"/>
+      <c r="AY35" s="15"/>
+      <c r="AZ35" s="15"/>
+    </row>
+    <row r="36" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A36" s="17"/>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -16694,22 +16980,30 @@
       <c r="AB36" s="15"/>
       <c r="AC36" s="15"/>
       <c r="AD36" s="15"/>
-      <c r="AE36" s="15"/>
-      <c r="AF36" s="15"/>
-      <c r="AG36" s="15"/>
-      <c r="AH36" s="15"/>
+      <c r="AE36" s="16"/>
+      <c r="AF36" s="16"/>
+      <c r="AG36" s="16"/>
+      <c r="AH36" s="16"/>
       <c r="AI36" s="15"/>
       <c r="AJ36" s="15"/>
       <c r="AK36" s="15"/>
       <c r="AL36" s="15"/>
       <c r="AM36" s="15"/>
       <c r="AN36" s="15"/>
-      <c r="AO36" s="28"/>
+      <c r="AO36" s="15"/>
       <c r="AP36" s="15"/>
       <c r="AQ36" s="15"/>
       <c r="AR36" s="15"/>
-    </row>
-    <row r="37" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS36" s="15"/>
+      <c r="AT36" s="15"/>
+      <c r="AU36" s="15"/>
+      <c r="AV36" s="15"/>
+      <c r="AW36" s="28"/>
+      <c r="AX36" s="15"/>
+      <c r="AY36" s="15"/>
+      <c r="AZ36" s="15"/>
+    </row>
+    <row r="37" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A37" s="17"/>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -16740,22 +17034,30 @@
       <c r="AB37" s="15"/>
       <c r="AC37" s="15"/>
       <c r="AD37" s="15"/>
-      <c r="AE37" s="15"/>
-      <c r="AF37" s="15"/>
-      <c r="AG37" s="15"/>
-      <c r="AH37" s="15"/>
+      <c r="AE37" s="16"/>
+      <c r="AF37" s="16"/>
+      <c r="AG37" s="16"/>
+      <c r="AH37" s="16"/>
       <c r="AI37" s="15"/>
       <c r="AJ37" s="15"/>
       <c r="AK37" s="15"/>
       <c r="AL37" s="15"/>
       <c r="AM37" s="15"/>
       <c r="AN37" s="15"/>
-      <c r="AO37" s="28"/>
+      <c r="AO37" s="15"/>
       <c r="AP37" s="15"/>
       <c r="AQ37" s="15"/>
       <c r="AR37" s="15"/>
-    </row>
-    <row r="38" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS37" s="15"/>
+      <c r="AT37" s="15"/>
+      <c r="AU37" s="15"/>
+      <c r="AV37" s="15"/>
+      <c r="AW37" s="28"/>
+      <c r="AX37" s="15"/>
+      <c r="AY37" s="15"/>
+      <c r="AZ37" s="15"/>
+    </row>
+    <row r="38" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A38" s="17"/>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -16786,22 +17088,30 @@
       <c r="AB38" s="15"/>
       <c r="AC38" s="15"/>
       <c r="AD38" s="15"/>
-      <c r="AE38" s="15"/>
-      <c r="AF38" s="15"/>
-      <c r="AG38" s="15"/>
-      <c r="AH38" s="15"/>
+      <c r="AE38" s="16"/>
+      <c r="AF38" s="16"/>
+      <c r="AG38" s="16"/>
+      <c r="AH38" s="16"/>
       <c r="AI38" s="15"/>
       <c r="AJ38" s="15"/>
       <c r="AK38" s="15"/>
       <c r="AL38" s="15"/>
       <c r="AM38" s="15"/>
       <c r="AN38" s="15"/>
-      <c r="AO38" s="28"/>
+      <c r="AO38" s="15"/>
       <c r="AP38" s="15"/>
       <c r="AQ38" s="15"/>
       <c r="AR38" s="15"/>
-    </row>
-    <row r="39" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS38" s="15"/>
+      <c r="AT38" s="15"/>
+      <c r="AU38" s="15"/>
+      <c r="AV38" s="15"/>
+      <c r="AW38" s="28"/>
+      <c r="AX38" s="15"/>
+      <c r="AY38" s="15"/>
+      <c r="AZ38" s="15"/>
+    </row>
+    <row r="39" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A39" s="17"/>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -16832,22 +17142,30 @@
       <c r="AB39" s="15"/>
       <c r="AC39" s="15"/>
       <c r="AD39" s="15"/>
-      <c r="AE39" s="15"/>
-      <c r="AF39" s="15"/>
-      <c r="AG39" s="15"/>
-      <c r="AH39" s="15"/>
+      <c r="AE39" s="16"/>
+      <c r="AF39" s="16"/>
+      <c r="AG39" s="16"/>
+      <c r="AH39" s="16"/>
       <c r="AI39" s="15"/>
       <c r="AJ39" s="15"/>
       <c r="AK39" s="15"/>
       <c r="AL39" s="15"/>
       <c r="AM39" s="15"/>
       <c r="AN39" s="15"/>
-      <c r="AO39" s="28"/>
+      <c r="AO39" s="15"/>
       <c r="AP39" s="15"/>
       <c r="AQ39" s="15"/>
       <c r="AR39" s="15"/>
-    </row>
-    <row r="40" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS39" s="15"/>
+      <c r="AT39" s="15"/>
+      <c r="AU39" s="15"/>
+      <c r="AV39" s="15"/>
+      <c r="AW39" s="28"/>
+      <c r="AX39" s="15"/>
+      <c r="AY39" s="15"/>
+      <c r="AZ39" s="15"/>
+    </row>
+    <row r="40" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A40" s="17"/>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -16878,22 +17196,30 @@
       <c r="AB40" s="15"/>
       <c r="AC40" s="15"/>
       <c r="AD40" s="15"/>
-      <c r="AE40" s="15"/>
-      <c r="AF40" s="15"/>
-      <c r="AG40" s="15"/>
-      <c r="AH40" s="15"/>
+      <c r="AE40" s="16"/>
+      <c r="AF40" s="16"/>
+      <c r="AG40" s="16"/>
+      <c r="AH40" s="16"/>
       <c r="AI40" s="15"/>
       <c r="AJ40" s="15"/>
       <c r="AK40" s="15"/>
       <c r="AL40" s="15"/>
       <c r="AM40" s="15"/>
       <c r="AN40" s="15"/>
-      <c r="AO40" s="28"/>
+      <c r="AO40" s="15"/>
       <c r="AP40" s="15"/>
       <c r="AQ40" s="15"/>
       <c r="AR40" s="15"/>
-    </row>
-    <row r="41" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS40" s="15"/>
+      <c r="AT40" s="15"/>
+      <c r="AU40" s="15"/>
+      <c r="AV40" s="15"/>
+      <c r="AW40" s="28"/>
+      <c r="AX40" s="15"/>
+      <c r="AY40" s="15"/>
+      <c r="AZ40" s="15"/>
+    </row>
+    <row r="41" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A41" s="17"/>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -16924,22 +17250,30 @@
       <c r="AB41" s="15"/>
       <c r="AC41" s="15"/>
       <c r="AD41" s="15"/>
-      <c r="AE41" s="15"/>
-      <c r="AF41" s="15"/>
-      <c r="AG41" s="15"/>
-      <c r="AH41" s="15"/>
+      <c r="AE41" s="16"/>
+      <c r="AF41" s="16"/>
+      <c r="AG41" s="16"/>
+      <c r="AH41" s="16"/>
       <c r="AI41" s="15"/>
       <c r="AJ41" s="15"/>
       <c r="AK41" s="15"/>
       <c r="AL41" s="15"/>
       <c r="AM41" s="15"/>
       <c r="AN41" s="15"/>
-      <c r="AO41" s="28"/>
+      <c r="AO41" s="15"/>
       <c r="AP41" s="15"/>
       <c r="AQ41" s="15"/>
       <c r="AR41" s="15"/>
-    </row>
-    <row r="42" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS41" s="15"/>
+      <c r="AT41" s="15"/>
+      <c r="AU41" s="15"/>
+      <c r="AV41" s="15"/>
+      <c r="AW41" s="28"/>
+      <c r="AX41" s="15"/>
+      <c r="AY41" s="15"/>
+      <c r="AZ41" s="15"/>
+    </row>
+    <row r="42" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A42" s="17"/>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -16970,22 +17304,30 @@
       <c r="AB42" s="15"/>
       <c r="AC42" s="15"/>
       <c r="AD42" s="15"/>
-      <c r="AE42" s="15"/>
-      <c r="AF42" s="15"/>
-      <c r="AG42" s="15"/>
-      <c r="AH42" s="15"/>
+      <c r="AE42" s="16"/>
+      <c r="AF42" s="16"/>
+      <c r="AG42" s="16"/>
+      <c r="AH42" s="16"/>
       <c r="AI42" s="15"/>
       <c r="AJ42" s="15"/>
       <c r="AK42" s="15"/>
       <c r="AL42" s="15"/>
       <c r="AM42" s="15"/>
       <c r="AN42" s="15"/>
-      <c r="AO42" s="28"/>
+      <c r="AO42" s="15"/>
       <c r="AP42" s="15"/>
       <c r="AQ42" s="15"/>
       <c r="AR42" s="15"/>
-    </row>
-    <row r="43" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS42" s="15"/>
+      <c r="AT42" s="15"/>
+      <c r="AU42" s="15"/>
+      <c r="AV42" s="15"/>
+      <c r="AW42" s="28"/>
+      <c r="AX42" s="15"/>
+      <c r="AY42" s="15"/>
+      <c r="AZ42" s="15"/>
+    </row>
+    <row r="43" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A43" s="17"/>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -17016,22 +17358,30 @@
       <c r="AB43" s="15"/>
       <c r="AC43" s="15"/>
       <c r="AD43" s="15"/>
-      <c r="AE43" s="15"/>
-      <c r="AF43" s="15"/>
-      <c r="AG43" s="15"/>
-      <c r="AH43" s="15"/>
+      <c r="AE43" s="16"/>
+      <c r="AF43" s="16"/>
+      <c r="AG43" s="16"/>
+      <c r="AH43" s="16"/>
       <c r="AI43" s="15"/>
       <c r="AJ43" s="15"/>
       <c r="AK43" s="15"/>
       <c r="AL43" s="15"/>
       <c r="AM43" s="15"/>
       <c r="AN43" s="15"/>
-      <c r="AO43" s="28"/>
+      <c r="AO43" s="15"/>
       <c r="AP43" s="15"/>
       <c r="AQ43" s="15"/>
       <c r="AR43" s="15"/>
-    </row>
-    <row r="44" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS43" s="15"/>
+      <c r="AT43" s="15"/>
+      <c r="AU43" s="15"/>
+      <c r="AV43" s="15"/>
+      <c r="AW43" s="28"/>
+      <c r="AX43" s="15"/>
+      <c r="AY43" s="15"/>
+      <c r="AZ43" s="15"/>
+    </row>
+    <row r="44" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A44" s="17"/>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -17062,22 +17412,30 @@
       <c r="AB44" s="15"/>
       <c r="AC44" s="15"/>
       <c r="AD44" s="15"/>
-      <c r="AE44" s="15"/>
-      <c r="AF44" s="15"/>
-      <c r="AG44" s="15"/>
-      <c r="AH44" s="15"/>
+      <c r="AE44" s="16"/>
+      <c r="AF44" s="16"/>
+      <c r="AG44" s="16"/>
+      <c r="AH44" s="16"/>
       <c r="AI44" s="15"/>
       <c r="AJ44" s="15"/>
       <c r="AK44" s="15"/>
       <c r="AL44" s="15"/>
       <c r="AM44" s="15"/>
       <c r="AN44" s="15"/>
-      <c r="AO44" s="28"/>
+      <c r="AO44" s="15"/>
       <c r="AP44" s="15"/>
       <c r="AQ44" s="15"/>
       <c r="AR44" s="15"/>
-    </row>
-    <row r="45" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS44" s="15"/>
+      <c r="AT44" s="15"/>
+      <c r="AU44" s="15"/>
+      <c r="AV44" s="15"/>
+      <c r="AW44" s="28"/>
+      <c r="AX44" s="15"/>
+      <c r="AY44" s="15"/>
+      <c r="AZ44" s="15"/>
+    </row>
+    <row r="45" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A45" s="17"/>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -17108,22 +17466,30 @@
       <c r="AB45" s="15"/>
       <c r="AC45" s="15"/>
       <c r="AD45" s="15"/>
-      <c r="AE45" s="15"/>
-      <c r="AF45" s="15"/>
-      <c r="AG45" s="15"/>
-      <c r="AH45" s="15"/>
+      <c r="AE45" s="16"/>
+      <c r="AF45" s="16"/>
+      <c r="AG45" s="16"/>
+      <c r="AH45" s="16"/>
       <c r="AI45" s="15"/>
       <c r="AJ45" s="15"/>
       <c r="AK45" s="15"/>
       <c r="AL45" s="15"/>
       <c r="AM45" s="15"/>
       <c r="AN45" s="15"/>
-      <c r="AO45" s="28"/>
+      <c r="AO45" s="15"/>
       <c r="AP45" s="15"/>
       <c r="AQ45" s="15"/>
       <c r="AR45" s="15"/>
-    </row>
-    <row r="46" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS45" s="15"/>
+      <c r="AT45" s="15"/>
+      <c r="AU45" s="15"/>
+      <c r="AV45" s="15"/>
+      <c r="AW45" s="28"/>
+      <c r="AX45" s="15"/>
+      <c r="AY45" s="15"/>
+      <c r="AZ45" s="15"/>
+    </row>
+    <row r="46" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A46" s="17"/>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -17154,22 +17520,30 @@
       <c r="AB46" s="15"/>
       <c r="AC46" s="15"/>
       <c r="AD46" s="15"/>
-      <c r="AE46" s="15"/>
-      <c r="AF46" s="15"/>
-      <c r="AG46" s="15"/>
-      <c r="AH46" s="15"/>
+      <c r="AE46" s="16"/>
+      <c r="AF46" s="16"/>
+      <c r="AG46" s="16"/>
+      <c r="AH46" s="16"/>
       <c r="AI46" s="15"/>
       <c r="AJ46" s="15"/>
       <c r="AK46" s="15"/>
       <c r="AL46" s="15"/>
       <c r="AM46" s="15"/>
       <c r="AN46" s="15"/>
-      <c r="AO46" s="28"/>
+      <c r="AO46" s="15"/>
       <c r="AP46" s="15"/>
       <c r="AQ46" s="15"/>
       <c r="AR46" s="15"/>
-    </row>
-    <row r="47" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS46" s="15"/>
+      <c r="AT46" s="15"/>
+      <c r="AU46" s="15"/>
+      <c r="AV46" s="15"/>
+      <c r="AW46" s="28"/>
+      <c r="AX46" s="15"/>
+      <c r="AY46" s="15"/>
+      <c r="AZ46" s="15"/>
+    </row>
+    <row r="47" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A47" s="17"/>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -17200,22 +17574,30 @@
       <c r="AB47" s="15"/>
       <c r="AC47" s="15"/>
       <c r="AD47" s="15"/>
-      <c r="AE47" s="15"/>
-      <c r="AF47" s="15"/>
-      <c r="AG47" s="15"/>
-      <c r="AH47" s="15"/>
+      <c r="AE47" s="16"/>
+      <c r="AF47" s="16"/>
+      <c r="AG47" s="16"/>
+      <c r="AH47" s="16"/>
       <c r="AI47" s="15"/>
       <c r="AJ47" s="15"/>
       <c r="AK47" s="15"/>
       <c r="AL47" s="15"/>
       <c r="AM47" s="15"/>
       <c r="AN47" s="15"/>
-      <c r="AO47" s="28"/>
+      <c r="AO47" s="15"/>
       <c r="AP47" s="15"/>
       <c r="AQ47" s="15"/>
       <c r="AR47" s="15"/>
-    </row>
-    <row r="48" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS47" s="15"/>
+      <c r="AT47" s="15"/>
+      <c r="AU47" s="15"/>
+      <c r="AV47" s="15"/>
+      <c r="AW47" s="28"/>
+      <c r="AX47" s="15"/>
+      <c r="AY47" s="15"/>
+      <c r="AZ47" s="15"/>
+    </row>
+    <row r="48" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A48" s="17"/>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -17246,22 +17628,30 @@
       <c r="AB48" s="15"/>
       <c r="AC48" s="15"/>
       <c r="AD48" s="15"/>
-      <c r="AE48" s="15"/>
-      <c r="AF48" s="15"/>
-      <c r="AG48" s="15"/>
-      <c r="AH48" s="15"/>
+      <c r="AE48" s="16"/>
+      <c r="AF48" s="16"/>
+      <c r="AG48" s="16"/>
+      <c r="AH48" s="16"/>
       <c r="AI48" s="15"/>
       <c r="AJ48" s="15"/>
       <c r="AK48" s="15"/>
       <c r="AL48" s="15"/>
       <c r="AM48" s="15"/>
       <c r="AN48" s="15"/>
-      <c r="AO48" s="28"/>
+      <c r="AO48" s="15"/>
       <c r="AP48" s="15"/>
       <c r="AQ48" s="15"/>
       <c r="AR48" s="15"/>
-    </row>
-    <row r="49" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS48" s="15"/>
+      <c r="AT48" s="15"/>
+      <c r="AU48" s="15"/>
+      <c r="AV48" s="15"/>
+      <c r="AW48" s="28"/>
+      <c r="AX48" s="15"/>
+      <c r="AY48" s="15"/>
+      <c r="AZ48" s="15"/>
+    </row>
+    <row r="49" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A49" s="17"/>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -17292,22 +17682,30 @@
       <c r="AB49" s="15"/>
       <c r="AC49" s="15"/>
       <c r="AD49" s="15"/>
-      <c r="AE49" s="15"/>
-      <c r="AF49" s="15"/>
-      <c r="AG49" s="15"/>
-      <c r="AH49" s="15"/>
+      <c r="AE49" s="16"/>
+      <c r="AF49" s="16"/>
+      <c r="AG49" s="16"/>
+      <c r="AH49" s="16"/>
       <c r="AI49" s="15"/>
       <c r="AJ49" s="15"/>
       <c r="AK49" s="15"/>
       <c r="AL49" s="15"/>
       <c r="AM49" s="15"/>
       <c r="AN49" s="15"/>
-      <c r="AO49" s="28"/>
+      <c r="AO49" s="15"/>
       <c r="AP49" s="15"/>
       <c r="AQ49" s="15"/>
       <c r="AR49" s="15"/>
-    </row>
-    <row r="50" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS49" s="15"/>
+      <c r="AT49" s="15"/>
+      <c r="AU49" s="15"/>
+      <c r="AV49" s="15"/>
+      <c r="AW49" s="28"/>
+      <c r="AX49" s="15"/>
+      <c r="AY49" s="15"/>
+      <c r="AZ49" s="15"/>
+    </row>
+    <row r="50" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A50" s="17"/>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -17338,22 +17736,30 @@
       <c r="AB50" s="15"/>
       <c r="AC50" s="15"/>
       <c r="AD50" s="15"/>
-      <c r="AE50" s="15"/>
-      <c r="AF50" s="15"/>
-      <c r="AG50" s="15"/>
-      <c r="AH50" s="15"/>
+      <c r="AE50" s="16"/>
+      <c r="AF50" s="16"/>
+      <c r="AG50" s="16"/>
+      <c r="AH50" s="16"/>
       <c r="AI50" s="15"/>
       <c r="AJ50" s="15"/>
       <c r="AK50" s="15"/>
       <c r="AL50" s="15"/>
       <c r="AM50" s="15"/>
       <c r="AN50" s="15"/>
-      <c r="AO50" s="28"/>
+      <c r="AO50" s="15"/>
       <c r="AP50" s="15"/>
       <c r="AQ50" s="15"/>
       <c r="AR50" s="15"/>
-    </row>
-    <row r="51" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS50" s="15"/>
+      <c r="AT50" s="15"/>
+      <c r="AU50" s="15"/>
+      <c r="AV50" s="15"/>
+      <c r="AW50" s="28"/>
+      <c r="AX50" s="15"/>
+      <c r="AY50" s="15"/>
+      <c r="AZ50" s="15"/>
+    </row>
+    <row r="51" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A51" s="17"/>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -17384,22 +17790,30 @@
       <c r="AB51" s="15"/>
       <c r="AC51" s="15"/>
       <c r="AD51" s="15"/>
-      <c r="AE51" s="15"/>
-      <c r="AF51" s="15"/>
-      <c r="AG51" s="15"/>
-      <c r="AH51" s="15"/>
+      <c r="AE51" s="16"/>
+      <c r="AF51" s="16"/>
+      <c r="AG51" s="16"/>
+      <c r="AH51" s="16"/>
       <c r="AI51" s="15"/>
       <c r="AJ51" s="15"/>
       <c r="AK51" s="15"/>
       <c r="AL51" s="15"/>
       <c r="AM51" s="15"/>
       <c r="AN51" s="15"/>
-      <c r="AO51" s="28"/>
+      <c r="AO51" s="15"/>
       <c r="AP51" s="15"/>
       <c r="AQ51" s="15"/>
       <c r="AR51" s="15"/>
-    </row>
-    <row r="52" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="AS51" s="15"/>
+      <c r="AT51" s="15"/>
+      <c r="AU51" s="15"/>
+      <c r="AV51" s="15"/>
+      <c r="AW51" s="28"/>
+      <c r="AX51" s="15"/>
+      <c r="AY51" s="15"/>
+      <c r="AZ51" s="15"/>
+    </row>
+    <row r="52" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A52" s="17"/>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -17430,20 +17844,28 @@
       <c r="AB52" s="15"/>
       <c r="AC52" s="15"/>
       <c r="AD52" s="15"/>
-      <c r="AE52" s="15"/>
-      <c r="AF52" s="15"/>
-      <c r="AG52" s="15"/>
-      <c r="AH52" s="15"/>
+      <c r="AE52" s="16"/>
+      <c r="AF52" s="16"/>
+      <c r="AG52" s="16"/>
+      <c r="AH52" s="16"/>
       <c r="AI52" s="15"/>
       <c r="AJ52" s="15"/>
       <c r="AK52" s="15"/>
       <c r="AL52" s="15"/>
       <c r="AM52" s="15"/>
       <c r="AN52" s="15"/>
-      <c r="AO52" s="28"/>
+      <c r="AO52" s="15"/>
       <c r="AP52" s="15"/>
       <c r="AQ52" s="15"/>
       <c r="AR52" s="15"/>
+      <c r="AS52" s="15"/>
+      <c r="AT52" s="15"/>
+      <c r="AU52" s="15"/>
+      <c r="AV52" s="15"/>
+      <c r="AW52" s="28"/>
+      <c r="AX52" s="15"/>
+      <c r="AY52" s="15"/>
+      <c r="AZ52" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -17458,14 +17880,14 @@
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="14">
+  <dataValidations count="17">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Unique" prompt="A value must be unique within the dataset" sqref="H17:H52" xr:uid="{274C493E-CBE0-2742-BFD6-A161E5736B5A}">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C17:C52" xr:uid="{792BC06D-75E6-1A4B-8EE7-26D8A0C4CF46}">
       <formula1>"string,number,integer,boolean,array,object,timestamp,date,time,map,vector"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" sqref="B17:B52 J17:L52 O17:W52 Y17:AR52" xr:uid="{DDC4FF9F-5023-E04B-9FAD-8E0C431863DF}"/>
+    <dataValidation allowBlank="1" sqref="B17:B52 J17:L52 O17:W52 Y17:AM52 AR17:AS52 AU17:AZ52" xr:uid="{DDC4FF9F-5023-E04B-9FAD-8E0C431863DF}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Required" prompt="Is this a required field (true) or can it be optional (false)" sqref="G17:G52" xr:uid="{653181B6-028C-9348-B6A1-78F7EF7B9A52}">
       <formula1>"true,false"</formula1>
     </dataValidation>
@@ -17481,15 +17903,24 @@
     <dataValidation type="list" allowBlank="1" sqref="X17:X52" xr:uid="{17C32F0F-20AB-664B-ABCA-B45524F93539}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Comments" prompt="Use this for internal comments, open questions, discussion points. _x000a_This will not become part of the ODCS YAML." sqref="AO16" xr:uid="{D669647A-617C-7549-9EA2-AC37BFEA6E41}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Comments" prompt="Use this for internal comments, open questions, discussion points. _x000a_This will not become part of the ODCS YAML." sqref="AW16" xr:uid="{D669647A-617C-7549-9EA2-AC37BFEA6E41}"/>
     <dataValidation type="list" allowBlank="1" sqref="K17:K103" xr:uid="{FC6EF137-EF73-574C-95CF-B57336C59E8E}">
       <formula1>"column,measure,dimension"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="L17:L103" xr:uid="{A061E7B4-4C11-5241-BD09-1677165B8299}">
+    <dataValidation type="list" allowBlank="1" sqref="L17:L103 AQ17:AQ100 AT17:AT100" xr:uid="{A061E7B4-4C11-5241-BD09-1677165B8299}">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14:E14" xr:uid="{D05E7DD6-9150-B941-B705-FF6CFA22D7F9}">
       <formula1>"true,false"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="AO17:AO100" xr:uid="{95DD2EA0-6986-414F-8048-0D9B55450EB2}">
+      <formula1>"bfloat16,binary,float16,float32,float64,int8,uint8"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="AP17:AP100" xr:uid="{EF98B3E8-396D-0F48-A972-E0956219870A}">
+      <formula1>"cosine,dotProduct,euclidean,hamming,manhattan"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" sqref="AN17:AN100" xr:uid="{F44F2772-48BF-B94D-9469-EC67E27A68CF}">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18640,65 +19071,65 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD55E6DF-E5C5-C142-BA93-791862A30BE7}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.1640625" style="2" customWidth="1"/>
     <col min="2" max="3" width="59.6640625" style="2" customWidth="1"/>
-    <col min="4" max="7" width="23.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="23.5" style="2" customWidth="1"/>
-    <col min="9" max="11" width="15.83203125" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="8.83203125" style="2"/>
+    <col min="4" max="8" width="23.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.5" style="2" customWidth="1"/>
+    <col min="10" max="12" width="15.83203125" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>156</v>
       </c>
       <c r="B4" s="5"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="5"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="5"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="I9" s="19" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J9" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="20"/>
       <c r="K9" s="20"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="20"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>62</v>
       </c>
@@ -18712,245 +19143,265 @@
         <v>63</v>
       </c>
       <c r="E10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="G10" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="H10" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="I10" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="10"/>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="10"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="15"/>
+      <c r="I11" s="5"/>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="15"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="5"/>
-      <c r="I12" s="15"/>
+      <c r="I12" s="5"/>
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="15"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
       <c r="H13" s="5"/>
-      <c r="I13" s="15"/>
+      <c r="I13" s="5"/>
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="15"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
       <c r="H14" s="5"/>
-      <c r="I14" s="15"/>
+      <c r="I14" s="5"/>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="15"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
       <c r="H15" s="5"/>
-      <c r="I15" s="15"/>
+      <c r="I15" s="5"/>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="15"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
       <c r="H16" s="5"/>
-      <c r="I16" s="15"/>
+      <c r="I16" s="5"/>
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="15"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
       <c r="H17" s="5"/>
-      <c r="I17" s="15"/>
+      <c r="I17" s="5"/>
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="15"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
       <c r="H18" s="5"/>
-      <c r="I18" s="15"/>
+      <c r="I18" s="5"/>
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="15"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
       <c r="H19" s="5"/>
-      <c r="I19" s="15"/>
+      <c r="I19" s="5"/>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="15"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
       <c r="H20" s="5"/>
-      <c r="I20" s="15"/>
+      <c r="I20" s="5"/>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="15"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
       <c r="H21" s="5"/>
-      <c r="I21" s="15"/>
+      <c r="I21" s="5"/>
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="15"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
       <c r="H22" s="5"/>
-      <c r="I22" s="15"/>
+      <c r="I22" s="5"/>
       <c r="J22" s="15"/>
       <c r="K22" s="15"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="15"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
       <c r="H23" s="5"/>
-      <c r="I23" s="15"/>
+      <c r="I23" s="5"/>
       <c r="J23" s="15"/>
       <c r="K23" s="15"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="15"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
       <c r="H24" s="5"/>
-      <c r="I24" s="15"/>
+      <c r="I24" s="5"/>
       <c r="J24" s="15"/>
       <c r="K24" s="15"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="15"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
       <c r="H25" s="5"/>
-      <c r="I25" s="15"/>
+      <c r="I25" s="5"/>
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="15"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
       <c r="H26" s="5"/>
-      <c r="I26" s="15"/>
+      <c r="I26" s="5"/>
       <c r="J26" s="15"/>
       <c r="K26" s="15"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="15"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
       <c r="H27" s="5"/>
-      <c r="I27" s="15"/>
+      <c r="I27" s="5"/>
       <c r="J27" s="15"/>
       <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="B11:G67 H11:K27" xr:uid="{8BD676B5-0F0C-9D41-BB36-24C33963E434}"/>
+    <dataValidation allowBlank="1" sqref="B11:H67 I11:L27" xr:uid="{8BD676B5-0F0C-9D41-BB36-24C33963E434}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/odcs-template-v3.2.xlsx
+++ b/odcs-template-v3.2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakob/entropyData/open-data-contract-standard-excel-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3875D753-AACC-B04A-B375-AAA28B30B143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20183E6F-6333-DF4B-A803-E6DEE385A976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="-33240" windowWidth="60160" windowHeight="33240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="8" r:id="rId1"/>
@@ -61,17 +61,18 @@
     <definedName name="quality">Quality!$A$4:$BF$300</definedName>
     <definedName name="relationships">Relationships!$A$4:$AZ$300</definedName>
     <definedName name="roles" localSheetId="7">Roles!$A$4:$AZ$1000</definedName>
-    <definedName name="schema.businessName" localSheetId="2">'Schema &lt;table_name&gt;'!$B$8</definedName>
-    <definedName name="schema.context.instructions" localSheetId="2">'Schema &lt;table_name&gt;'!$B$13</definedName>
-    <definedName name="schema.dataGranularityDescription" localSheetId="2">'Schema &lt;table_name&gt;'!$B$10</definedName>
-    <definedName name="schema.deprecated" localSheetId="2">'Schema &lt;table_name&gt;'!$B$14</definedName>
-    <definedName name="schema.description" localSheetId="2">'Schema &lt;table_name&gt;'!$B$7</definedName>
-    <definedName name="schema.id" localSheetId="2">'Schema &lt;table_name&gt;'!$B$12</definedName>
+    <definedName name="schema.businessName" localSheetId="2">'Schema &lt;table_name&gt;'!$B$9</definedName>
+    <definedName name="schema.context.instructions" localSheetId="2">'Schema &lt;table_name&gt;'!$B$14</definedName>
+    <definedName name="schema.dataGranularityDescription" localSheetId="2">'Schema &lt;table_name&gt;'!$B$11</definedName>
+    <definedName name="schema.deprecated" localSheetId="2">'Schema &lt;table_name&gt;'!$B$15</definedName>
+    <definedName name="schema.description" localSheetId="2">'Schema &lt;table_name&gt;'!$B$8</definedName>
+    <definedName name="schema.id" localSheetId="2">'Schema &lt;table_name&gt;'!$B$13</definedName>
+    <definedName name="schema.logicalType" localSheetId="2">'Schema &lt;table_name&gt;'!$B$7</definedName>
     <definedName name="schema.name" localSheetId="2">'Schema &lt;table_name&gt;'!$B$5</definedName>
-    <definedName name="schema.physicalName" localSheetId="2">'Schema &lt;table_name&gt;'!$B$9</definedName>
+    <definedName name="schema.physicalName" localSheetId="2">'Schema &lt;table_name&gt;'!$B$10</definedName>
     <definedName name="schema.physicalType" localSheetId="2">'Schema &lt;table_name&gt;'!$B$6</definedName>
-    <definedName name="schema.properties" localSheetId="2">'Schema &lt;table_name&gt;'!$A$16:$AW$984</definedName>
-    <definedName name="schema.tags" localSheetId="2">'Schema &lt;table_name&gt;'!$B$11</definedName>
+    <definedName name="schema.properties" localSheetId="2">'Schema &lt;table_name&gt;'!$A$17:$AW$985</definedName>
+    <definedName name="schema.tags" localSheetId="2">'Schema &lt;table_name&gt;'!$B$12</definedName>
     <definedName name="servers.account">Servers!$C$11</definedName>
     <definedName name="servers.catalog">Servers!$C$12</definedName>
     <definedName name="servers.catalogUrl">Servers!$C$13</definedName>
@@ -133,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="260">
   <si>
     <t>Property</t>
   </si>
@@ -1158,7 +1159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1246,12 +1247,6 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1262,6 +1257,21 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -15494,10 +15504,10 @@
       <c r="B12" s="7"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="36"/>
+      <c r="B13" s="43"/>
       <c r="C13" s="5"/>
       <c r="E13" s="6"/>
     </row>
@@ -15602,7 +15612,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AZ52"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.83203125" style="2" customWidth="1"/>
@@ -15648,334 +15658,289 @@
       <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
     </row>
     <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
     </row>
     <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="39"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="41"/>
     </row>
     <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="40"/>
+        <v>3</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
     </row>
     <row r="9" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="40"/>
+        <v>9</v>
+      </c>
+      <c r="B9" s="36"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="38"/>
     </row>
     <row r="10" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="40"/>
+        <v>51</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="38"/>
     </row>
     <row r="11" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="37"/>
+        <v>52</v>
+      </c>
+      <c r="B11" s="36"/>
       <c r="C11" s="37"/>
       <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
+      <c r="E11" s="38"/>
     </row>
     <row r="12" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
+        <v>12</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
     </row>
     <row r="13" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
+        <v>22</v>
+      </c>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
     </row>
     <row r="14" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-    </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="E15" s="2"/>
-      <c r="Y15" s="19" t="s">
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="E16" s="2"/>
+      <c r="Y16" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="Z15" s="20"/>
-      <c r="AA15" s="20"/>
-      <c r="AB15" s="20"/>
-      <c r="AC15" s="20"/>
-      <c r="AD15" s="20"/>
-      <c r="AE15" s="20"/>
-      <c r="AF15" s="20"/>
-      <c r="AG15" s="20"/>
-      <c r="AH15" s="20"/>
-      <c r="AI15" s="20"/>
-      <c r="AJ15" s="20"/>
-      <c r="AK15" s="20"/>
-      <c r="AL15" s="20"/>
-      <c r="AM15" s="20"/>
-      <c r="AN15" s="20"/>
-      <c r="AO15" s="20"/>
-      <c r="AP15" s="20"/>
-      <c r="AQ15" s="20"/>
-      <c r="AR15" s="20"/>
-      <c r="AS15" s="20"/>
-      <c r="AT15" s="20"/>
-      <c r="AU15" s="21"/>
-      <c r="AX15" s="19" t="s">
+      <c r="Z16" s="20"/>
+      <c r="AA16" s="20"/>
+      <c r="AB16" s="20"/>
+      <c r="AC16" s="20"/>
+      <c r="AD16" s="20"/>
+      <c r="AE16" s="20"/>
+      <c r="AF16" s="20"/>
+      <c r="AG16" s="20"/>
+      <c r="AH16" s="20"/>
+      <c r="AI16" s="20"/>
+      <c r="AJ16" s="20"/>
+      <c r="AK16" s="20"/>
+      <c r="AL16" s="20"/>
+      <c r="AM16" s="20"/>
+      <c r="AN16" s="20"/>
+      <c r="AO16" s="20"/>
+      <c r="AP16" s="20"/>
+      <c r="AQ16" s="20"/>
+      <c r="AR16" s="20"/>
+      <c r="AS16" s="20"/>
+      <c r="AT16" s="20"/>
+      <c r="AU16" s="21"/>
+      <c r="AX16" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="AY15" s="20"/>
-      <c r="AZ15" s="20"/>
-    </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
+      <c r="AY16" s="20"/>
+      <c r="AZ16" s="20"/>
+    </row>
+    <row r="17" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B17" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C17" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E17" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F17" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G17" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H17" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I17" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="J17" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K17" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="L16" s="10" t="s">
+      <c r="L17" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="M16" s="10" t="s">
+      <c r="M17" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N16" s="10" t="s">
+      <c r="N17" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O16" s="10" t="s">
+      <c r="O17" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="P16" s="10" t="s">
+      <c r="P17" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="Q16" s="10" t="s">
+      <c r="Q17" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="R16" s="10" t="s">
+      <c r="R17" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="S16" s="10" t="s">
+      <c r="S17" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="T16" s="10" t="s">
+      <c r="T17" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="U16" s="10" t="s">
+      <c r="U17" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="V16" s="10" t="s">
+      <c r="V17" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="W16" s="10" t="s">
+      <c r="W17" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="X16" s="10" t="s">
+      <c r="X17" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="Y16" s="10" t="s">
+      <c r="Y17" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="Z16" s="10" t="s">
+      <c r="Z17" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="AA16" s="10" t="s">
+      <c r="AA17" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AB16" s="10" t="s">
+      <c r="AB17" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="AC16" s="10" t="s">
+      <c r="AC17" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="AD16" s="10" t="s">
+      <c r="AD17" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="AE16" s="10" t="s">
+      <c r="AE17" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="AF16" s="10" t="s">
+      <c r="AF17" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="AG16" s="10" t="s">
+      <c r="AG17" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="AH16" s="10" t="s">
+      <c r="AH17" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="AI16" s="10" t="s">
+      <c r="AI17" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="AJ16" s="10" t="s">
+      <c r="AJ17" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="AK16" s="10" t="s">
+      <c r="AK17" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="AL16" s="10" t="s">
+      <c r="AL17" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="AM16" s="10" t="s">
+      <c r="AM17" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="AN16" s="10" t="s">
+      <c r="AN17" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="AO16" s="10" t="s">
+      <c r="AO17" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="AP16" s="10" t="s">
+      <c r="AP17" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="AQ16" s="10" t="s">
+      <c r="AQ17" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="AR16" s="10" t="s">
+      <c r="AR17" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="AS16" s="10" t="s">
+      <c r="AS17" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="AT16" s="10" t="s">
+      <c r="AT17" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="AU16" s="10" t="s">
+      <c r="AU17" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="AV16" s="10" t="s">
+      <c r="AV17" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="AW16" s="10" t="s">
+      <c r="AW17" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="AX16" s="10"/>
-      <c r="AY16" s="10"/>
-      <c r="AZ16" s="10"/>
-    </row>
-    <row r="17" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A17" s="17"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="15"/>
-      <c r="T17" s="15"/>
-      <c r="U17" s="15"/>
-      <c r="V17" s="15"/>
-      <c r="W17" s="15"/>
-      <c r="X17" s="15"/>
-      <c r="Y17" s="15"/>
-      <c r="Z17" s="15"/>
-      <c r="AA17" s="15"/>
-      <c r="AB17" s="15"/>
-      <c r="AC17" s="15"/>
-      <c r="AD17" s="15"/>
-      <c r="AE17" s="16"/>
-      <c r="AF17" s="16"/>
-      <c r="AG17" s="16"/>
-      <c r="AH17" s="16"/>
-      <c r="AI17" s="15"/>
-      <c r="AJ17" s="15"/>
-      <c r="AK17" s="15"/>
-      <c r="AL17" s="15"/>
-      <c r="AM17" s="15"/>
-      <c r="AN17" s="15"/>
-      <c r="AO17" s="15"/>
-      <c r="AP17" s="15"/>
-      <c r="AQ17" s="15"/>
-      <c r="AR17" s="15"/>
-      <c r="AS17" s="15"/>
-      <c r="AT17" s="15"/>
-      <c r="AU17" s="15"/>
-      <c r="AV17" s="15"/>
-      <c r="AW17" s="28"/>
-      <c r="AX17" s="15"/>
-      <c r="AY17" s="15"/>
-      <c r="AZ17" s="15"/>
+      <c r="AX17" s="10"/>
+      <c r="AY17" s="10"/>
+      <c r="AZ17" s="10"/>
     </row>
     <row r="18" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A18" s="17"/>
@@ -16302,7 +16267,7 @@
       <c r="AZ23" s="15"/>
     </row>
     <row r="24" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
+      <c r="A24" s="17"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -16464,7 +16429,7 @@
       <c r="AZ26" s="15"/>
     </row>
     <row r="27" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A27" s="17"/>
+      <c r="A27" s="18"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
@@ -17867,60 +17832,118 @@
       <c r="AY52" s="15"/>
       <c r="AZ52" s="15"/>
     </row>
+    <row r="53" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A53" s="17"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="15"/>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="15"/>
+      <c r="M53" s="15"/>
+      <c r="N53" s="15"/>
+      <c r="O53" s="15"/>
+      <c r="P53" s="15"/>
+      <c r="Q53" s="15"/>
+      <c r="R53" s="15"/>
+      <c r="S53" s="15"/>
+      <c r="T53" s="15"/>
+      <c r="U53" s="15"/>
+      <c r="V53" s="15"/>
+      <c r="W53" s="15"/>
+      <c r="X53" s="15"/>
+      <c r="Y53" s="15"/>
+      <c r="Z53" s="15"/>
+      <c r="AA53" s="15"/>
+      <c r="AB53" s="15"/>
+      <c r="AC53" s="15"/>
+      <c r="AD53" s="15"/>
+      <c r="AE53" s="16"/>
+      <c r="AF53" s="16"/>
+      <c r="AG53" s="16"/>
+      <c r="AH53" s="16"/>
+      <c r="AI53" s="15"/>
+      <c r="AJ53" s="15"/>
+      <c r="AK53" s="15"/>
+      <c r="AL53" s="15"/>
+      <c r="AM53" s="15"/>
+      <c r="AN53" s="15"/>
+      <c r="AO53" s="15"/>
+      <c r="AP53" s="15"/>
+      <c r="AQ53" s="15"/>
+      <c r="AR53" s="15"/>
+      <c r="AS53" s="15"/>
+      <c r="AT53" s="15"/>
+      <c r="AU53" s="15"/>
+      <c r="AV53" s="15"/>
+      <c r="AW53" s="28"/>
+      <c r="AX53" s="15"/>
+      <c r="AY53" s="15"/>
+      <c r="AZ53" s="15"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="B15:E15"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B12:E12"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B11:E11"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B12:E12"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B7:E7"/>
   </mergeCells>
-  <dataValidations count="17">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Unique" prompt="A value must be unique within the dataset" sqref="H17:H52" xr:uid="{274C493E-CBE0-2742-BFD6-A161E5736B5A}">
+  <dataValidations count="18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Unique" prompt="A value must be unique within the dataset" sqref="H18:H53" xr:uid="{274C493E-CBE0-2742-BFD6-A161E5736B5A}">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C17:C52" xr:uid="{792BC06D-75E6-1A4B-8EE7-26D8A0C4CF46}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C18:C53" xr:uid="{792BC06D-75E6-1A4B-8EE7-26D8A0C4CF46}">
       <formula1>"string,number,integer,boolean,array,object,timestamp,date,time,map,vector"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" sqref="B17:B52 J17:L52 O17:W52 Y17:AM52 AR17:AS52 AU17:AZ52" xr:uid="{DDC4FF9F-5023-E04B-9FAD-8E0C431863DF}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Required" prompt="Is this a required field (true) or can it be optional (false)" sqref="G17:G52" xr:uid="{653181B6-028C-9348-B6A1-78F7EF7B9A52}">
+    <dataValidation allowBlank="1" sqref="B18:B53 J18:L53 O18:W53 Y18:AM53 AR18:AS53 AU18:AZ53" xr:uid="{DDC4FF9F-5023-E04B-9FAD-8E0C431863DF}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Required" prompt="Is this a required field (true) or can it be optional (false)" sqref="G18:G53" xr:uid="{653181B6-028C-9348-B6A1-78F7EF7B9A52}">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Schema Name" prompt="The name of the schema (e.g., table) must match the Sheet name &quot;Schema &lt;schema_name&gt;&quot;" sqref="B5:E5" xr:uid="{8B3F718D-6361-B845-86DC-2F310C7348A9}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Property" prompt="Name of the property._x000a_If you have structured objects (child properties), use the dot notation, e.g., address.street._x000a_If you have array structures, use the [] notation, e.g., credit_cards[].number." sqref="A16" xr:uid="{0D2C99EC-1C07-E24C-A3B9-1D3DE4A213B3}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Authoritative Definition Type" prompt="Type of definition for authority. Valid values are: businessDefinition, transformationImplementation, videoTutorial, tutorial, and implementation._x000a_ Maps to first authoritativeDefinitions.type_x000a_" sqref="N17:N52" xr:uid="{B83703A8-BFB7-EA4A-8244-28C8F1668E20}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Property" prompt="Name of the property._x000a_If you have structured objects (child properties), use the dot notation, e.g., address.street._x000a_If you have array structures, use the [] notation, e.g., credit_cards[].number." sqref="A17" xr:uid="{0D2C99EC-1C07-E24C-A3B9-1D3DE4A213B3}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Authoritative Definition Type" prompt="Type of definition for authority. Valid values are: businessDefinition, transformationImplementation, videoTutorial, tutorial, and implementation._x000a_ Maps to first authoritativeDefinitions.type_x000a_" sqref="N18:N53" xr:uid="{B83703A8-BFB7-EA4A-8244-28C8F1668E20}">
       <formula1>"businessDefinition,canonicalUrl,glossary,implementation,ontology,taxonomy,transformationImplementation,tutorial,videoTutorial"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I17:I52" xr:uid="{159197B4-47E7-9F48-923A-42F63EFB1F97}">
+    <dataValidation type="list" allowBlank="1" sqref="I18:I53" xr:uid="{159197B4-47E7-9F48-923A-42F63EFB1F97}">
       <formula1>"confidential,restricted,public"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Authoritative Definition URL" prompt="Links to sources that provide more details on the element; examples would be a link to privacy statement, terms and conditions, license agreements, data catalog, or another tool._x000a__x000a_Maps to first authoritativeDefinitions.url_x000a_" sqref="M17:M52" xr:uid="{282580C6-13B6-1B40-9A3A-85842409A299}"/>
-    <dataValidation type="list" allowBlank="1" sqref="X17:X52" xr:uid="{17C32F0F-20AB-664B-ABCA-B45524F93539}">
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Authoritative Definition URL" prompt="Links to sources that provide more details on the element; examples would be a link to privacy statement, terms and conditions, license agreements, data catalog, or another tool._x000a__x000a_Maps to first authoritativeDefinitions.url_x000a_" sqref="M18:M53" xr:uid="{282580C6-13B6-1B40-9A3A-85842409A299}"/>
+    <dataValidation type="list" allowBlank="1" sqref="X18:X53" xr:uid="{17C32F0F-20AB-664B-ABCA-B45524F93539}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Comments" prompt="Use this for internal comments, open questions, discussion points. _x000a_This will not become part of the ODCS YAML." sqref="AW16" xr:uid="{D669647A-617C-7549-9EA2-AC37BFEA6E41}"/>
-    <dataValidation type="list" allowBlank="1" sqref="K17:K103" xr:uid="{FC6EF137-EF73-574C-95CF-B57336C59E8E}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Comments" prompt="Use this for internal comments, open questions, discussion points. _x000a_This will not become part of the ODCS YAML." sqref="AW17" xr:uid="{D669647A-617C-7549-9EA2-AC37BFEA6E41}"/>
+    <dataValidation type="list" allowBlank="1" sqref="K18:K104" xr:uid="{FC6EF137-EF73-574C-95CF-B57336C59E8E}">
       <formula1>"column,measure,dimension"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="L17:L103 AQ17:AQ100 AT17:AT100" xr:uid="{A061E7B4-4C11-5241-BD09-1677165B8299}">
+    <dataValidation type="list" allowBlank="1" sqref="L18:L104 AQ18:AQ101 AT18:AT101" xr:uid="{A061E7B4-4C11-5241-BD09-1677165B8299}">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14:E14" xr:uid="{D05E7DD6-9150-B941-B705-FF6CFA22D7F9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:E15" xr:uid="{D05E7DD6-9150-B941-B705-FF6CFA22D7F9}">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="AO17:AO100" xr:uid="{95DD2EA0-6986-414F-8048-0D9B55450EB2}">
+    <dataValidation type="list" allowBlank="1" sqref="AO18:AO101" xr:uid="{95DD2EA0-6986-414F-8048-0D9B55450EB2}">
       <formula1>"bfloat16,binary,float16,float32,float64,int8,uint8"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="AP17:AP100" xr:uid="{EF98B3E8-396D-0F48-A972-E0956219870A}">
+    <dataValidation type="list" allowBlank="1" sqref="AP18:AP101" xr:uid="{EF98B3E8-396D-0F48-A972-E0956219870A}">
       <formula1>"cosine,dotProduct,euclidean,hamming,manhattan"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" sqref="AN17:AN100" xr:uid="{F44F2772-48BF-B94D-9469-EC67E27A68CF}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" sqref="AN18:AN101" xr:uid="{F44F2772-48BF-B94D-9469-EC67E27A68CF}">
       <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:E7" xr:uid="{235F05D9-F9B3-6C48-A55D-32FE3C7AACA5}">
+      <formula1>"object,blob"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
